--- a/deliverables/05-electrical/CFU-000-EL-LDL-001_Electrical-Load-List.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-LDL-001_Electrical-Load-List.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y122"/>
+  <dimension ref="A1:Y126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1052,14 +1052,14 @@
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="6" t="n">
-        <v>188.85</v>
+        <v>267.54</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="M9" s="8" t="n">
         <v>0.955</v>
@@ -1068,13 +1068,13 @@
         <v>0.87</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>197.75</v>
+        <v>280.15</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>112.07</v>
+        <v>158.77</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>227.3</v>
+        <v>322.01</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>197.75</v>
+        <v>280.15</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="6" t="n">
-        <v>112.07</v>
+        <v>158.77</v>
       </c>
       <c r="Y9" s="4" t="inlineStr"/>
     </row>
@@ -1139,14 +1139,14 @@
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="6" t="n">
-        <v>188.85</v>
+        <v>267.54</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>0.955</v>
@@ -1155,13 +1155,13 @@
         <v>0.87</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>197.75</v>
+        <v>280.15</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>112.07</v>
+        <v>158.77</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>227.3</v>
+        <v>322.01</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="S10" s="6" t="n">
-        <v>197.75</v>
+        <v>280.15</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>112.07</v>
+        <v>158.77</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 1/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -4967,14 +4967,14 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="9" t="n">
-        <v>67.48999999999999</v>
+        <v>45</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>0.9350000000000001</v>
@@ -4983,13 +4983,13 @@
         <v>0.95</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="P54" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>78.34</v>
+        <v>52.22</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="S54" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 2/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5054,14 +5054,14 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="9" t="n">
-        <v>67.48999999999999</v>
+        <v>45</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>0.9350000000000001</v>
@@ -5070,13 +5070,13 @@
         <v>0.95</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="P55" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>78.34</v>
+        <v>52.22</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="S55" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 3/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5141,14 +5141,14 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="9" t="n">
-        <v>67.48999999999999</v>
+        <v>45</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M56" s="8" t="n">
         <v>0.9350000000000001</v>
@@ -5157,13 +5157,13 @@
         <v>0.95</v>
       </c>
       <c r="O56" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>78.34</v>
+        <v>52.22</v>
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="S56" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 4/4 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5228,14 +5228,14 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="9" t="n">
-        <v>67.48999999999999</v>
+        <v>45</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M57" s="8" t="n">
         <v>0.9350000000000001</v>
@@ -5244,13 +5244,13 @@
         <v>0.95</v>
       </c>
       <c r="O57" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="P57" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>78.34</v>
+        <v>52.22</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="S57" s="9" t="n">
-        <v>74.42</v>
+        <v>49.61</v>
       </c>
       <c r="T57" s="9" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>24.46</v>
+        <v>16.31</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -5283,17 +5283,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>A-103-M1</t>
+          <t>A-101-M5</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 1/2</t>
+          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>A-103</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>VFD</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -5315,29 +5315,29 @@
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="9" t="n">
-        <v>7.5</v>
+        <v>45</v>
       </c>
       <c r="L58" s="7" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="M58" s="8" t="n">
-        <v>0.91</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N58" s="7" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="O58" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="P58" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="Q58" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>52.22</v>
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="S58" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>A-103-M2</t>
+          <t>A-101-M6</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 2/2</t>
+          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A-103</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>VFD</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -5402,29 +5402,29 @@
         </is>
       </c>
       <c r="I59" s="9" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="9" t="n">
-        <v>7.5</v>
+        <v>45</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>0.91</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="P59" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>52.22</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="S59" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -5457,17 +5457,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>A-104-M1</t>
+          <t>A-103-M1</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 1/2</t>
+          <t>Kero cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>A-104</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5489,14 +5489,14 @@
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="9" t="n">
-        <v>14.89</v>
+        <v>7.5</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M60" s="8" t="n">
         <v>0.91</v>
@@ -5505,13 +5505,13 @@
         <v>0.85</v>
       </c>
       <c r="O60" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="P60" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>19.26</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="S60" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -5544,17 +5544,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>A-104-M2</t>
+          <t>A-103-M2</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 2/2</t>
+          <t>Kero cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A-104</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5576,14 +5576,14 @@
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="9" t="n">
-        <v>14.89</v>
+        <v>7.5</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M61" s="8" t="n">
         <v>0.91</v>
@@ -5592,13 +5592,13 @@
         <v>0.85</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="P61" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>19.26</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="S61" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>A-105-M1</t>
+          <t>A-104-M1</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 1/2</t>
+          <t>Diesel cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5663,11 +5663,11 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="9" t="n">
-        <v>24.23</v>
+        <v>14.89</v>
       </c>
       <c r="L62" s="7" t="n">
         <v>0.8100000000000001</v>
@@ -5679,13 +5679,13 @@
         <v>0.85</v>
       </c>
       <c r="O62" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="P62" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>31.33</v>
+        <v>19.26</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="S62" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>A-105-M2</t>
+          <t>A-104-M2</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 2/2</t>
+          <t>Diesel cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5750,11 +5750,11 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="9" t="n">
-        <v>24.23</v>
+        <v>14.89</v>
       </c>
       <c r="L63" s="7" t="n">
         <v>0.8100000000000001</v>
@@ -5766,13 +5766,13 @@
         <v>0.85</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="P63" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>31.33</v>
+        <v>19.26</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="S63" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>A-106-M1</t>
+          <t>A-105-M1</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 1/2</t>
+          <t>Ago cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -5837,14 +5837,14 @@
         </is>
       </c>
       <c r="I64" s="9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="9" t="n">
-        <v>8.550000000000001</v>
+        <v>24.23</v>
       </c>
       <c r="L64" s="7" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M64" s="8" t="n">
         <v>0.91</v>
@@ -5853,13 +5853,13 @@
         <v>0.85</v>
       </c>
       <c r="O64" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>11.06</v>
+        <v>31.33</v>
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="S64" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -5892,17 +5892,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>A-106-M2</t>
+          <t>A-105-M2</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 2/2</t>
+          <t>Ago cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5924,14 +5924,14 @@
         </is>
       </c>
       <c r="I65" s="9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="9" t="n">
-        <v>8.550000000000001</v>
+        <v>24.23</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M65" s="8" t="n">
         <v>0.91</v>
@@ -5940,13 +5940,13 @@
         <v>0.85</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="P65" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>11.06</v>
+        <v>31.33</v>
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="S65" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -5979,17 +5979,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>A-107-M1</t>
+          <t>A-106-M1</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 1/2</t>
+          <t>Stabiliser overhead condenser - fan motor 1/2</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>A-107</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -6011,29 +6011,29 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="9" t="n">
-        <v>38.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="M66" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N66" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>41.18</v>
+        <v>9.4</v>
       </c>
       <c r="P66" s="9" t="n">
-        <v>24.43</v>
+        <v>5.83</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>47.88</v>
+        <v>11.06</v>
       </c>
       <c r="R66" s="4" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="S66" s="9" t="n">
-        <v>41.18</v>
+        <v>9.4</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>24.43</v>
+        <v>5.83</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -6066,17 +6066,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>A-107-M2</t>
+          <t>A-106-M2</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 2/2</t>
+          <t>Stabiliser overhead condenser - fan motor 2/2</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A-107</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6098,29 +6098,29 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="9" t="n">
-        <v>38.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="M67" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>41.18</v>
+        <v>9.4</v>
       </c>
       <c r="P67" s="9" t="n">
-        <v>24.43</v>
+        <v>5.83</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>47.88</v>
+        <v>11.06</v>
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="S67" s="9" t="n">
-        <v>41.18</v>
+        <v>9.4</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>24.43</v>
+        <v>5.83</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>A-108-M1</t>
+          <t>A-107-M1</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 1/4</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -6189,10 +6189,10 @@
       </c>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="9" t="n">
-        <v>23.23</v>
+        <v>19.25</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M68" s="8" t="n">
         <v>0.91</v>
@@ -6201,13 +6201,13 @@
         <v>0.85</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="P68" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>30.04</v>
+        <v>24.89</v>
       </c>
       <c r="R68" s="4" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="S68" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -6240,17 +6240,17 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>A-108-M2</t>
+          <t>A-107-M2</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 2/4</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6276,10 +6276,10 @@
       </c>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="9" t="n">
-        <v>23.23</v>
+        <v>19.25</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M69" s="8" t="n">
         <v>0.91</v>
@@ -6288,13 +6288,13 @@
         <v>0.85</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="P69" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>30.04</v>
+        <v>24.89</v>
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="S69" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="T69" s="9" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -6327,17 +6327,17 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>A-201-M1</t>
+          <t>A-107-M3</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 3/4</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -6359,14 +6359,14 @@
         </is>
       </c>
       <c r="I70" s="9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="9" t="n">
-        <v>12.4</v>
+        <v>19.25</v>
       </c>
       <c r="L70" s="7" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="M70" s="8" t="n">
         <v>0.91</v>
@@ -6375,13 +6375,13 @@
         <v>0.85</v>
       </c>
       <c r="O70" s="9" t="n">
-        <v>13.62</v>
+        <v>21.16</v>
       </c>
       <c r="P70" s="9" t="n">
-        <v>8.44</v>
+        <v>13.11</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>16.02</v>
+        <v>24.89</v>
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="S70" s="9" t="n">
-        <v>13.62</v>
+        <v>21.16</v>
       </c>
       <c r="T70" s="9" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>8.44</v>
+        <v>13.11</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -6414,17 +6414,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>A-201-M2</t>
+          <t>A-107-M4</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 4/4</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6446,14 +6446,14 @@
         </is>
       </c>
       <c r="I71" s="9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="9" t="n">
-        <v>12.4</v>
+        <v>19.25</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="M71" s="8" t="n">
         <v>0.91</v>
@@ -6462,13 +6462,13 @@
         <v>0.85</v>
       </c>
       <c r="O71" s="9" t="n">
-        <v>13.62</v>
+        <v>21.16</v>
       </c>
       <c r="P71" s="9" t="n">
-        <v>8.44</v>
+        <v>13.11</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>16.02</v>
+        <v>24.89</v>
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="S71" s="9" t="n">
-        <v>13.62</v>
+        <v>21.16</v>
       </c>
       <c r="T71" s="9" t="n">
         <v>0</v>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>8.44</v>
+        <v>13.11</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -6501,17 +6501,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>A-202-M1</t>
+          <t>A-108-M1</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 1/2</t>
+          <t>Heavy naphtha product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -6533,29 +6533,29 @@
         </is>
       </c>
       <c r="I72" s="9" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="9" t="n">
-        <v>26.56</v>
+        <v>23.23</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="M72" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N72" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>28.41</v>
+        <v>25.53</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>16.86</v>
+        <v>15.82</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>33.03</v>
+        <v>30.04</v>
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="S72" s="9" t="n">
-        <v>28.41</v>
+        <v>25.53</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>16.86</v>
+        <v>15.82</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -6588,17 +6588,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>A-202-M2</t>
+          <t>A-108-M2</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 2/2</t>
+          <t>Heavy naphtha product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6620,29 +6620,29 @@
         </is>
       </c>
       <c r="I73" s="9" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="9" t="n">
-        <v>26.56</v>
+        <v>23.23</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="M73" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>28.41</v>
+        <v>25.53</v>
       </c>
       <c r="P73" s="9" t="n">
-        <v>16.86</v>
+        <v>15.82</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>33.03</v>
+        <v>30.04</v>
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="S73" s="9" t="n">
-        <v>28.41</v>
+        <v>25.53</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>16.86</v>
+        <v>15.82</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -6675,22 +6675,22 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>X-101-PA</t>
+          <t>A-201-M1</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump A</t>
+          <t>Lvgo cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
@@ -6707,29 +6707,29 @@
         </is>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0.75</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="9" t="n">
-        <v>0.45</v>
+        <v>12.4</v>
       </c>
       <c r="L74" s="7" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="N74" s="7" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0.48</v>
+        <v>8.44</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0.74</v>
+        <v>16.02</v>
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0.48</v>
+        <v>8.44</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -6754,11 +6754,7 @@
       <c r="X74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y74" s="4" t="inlineStr">
-        <is>
-          <t>2 x 100 % pumps per package</t>
-        </is>
-      </c>
+      <c r="Y74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -6766,22 +6762,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>X-101-PB</t>
+          <t>A-201-M2</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump B</t>
+          <t>Lvgo cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
@@ -6798,52 +6794,52 @@
         </is>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0.75</v>
+        <v>15</v>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="9" t="n">
-        <v>0.45</v>
+        <v>12.4</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="M75" s="8" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="O75" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>13.62</v>
       </c>
       <c r="P75" s="9" t="n">
-        <v>0.48</v>
+        <v>8.44</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0.74</v>
+        <v>16.02</v>
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S75" s="9" t="n">
-        <v>0</v>
+        <v>13.62</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U75" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>8.44</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X75" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="4" t="inlineStr"/>
     </row>
@@ -6853,22 +6849,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>X-102-PA</t>
+          <t>A-202-M1</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump A</t>
+          <t>Hvgo Product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
@@ -6885,29 +6881,29 @@
         </is>
       </c>
       <c r="I76" s="9" t="n">
-        <v>0.75</v>
+        <v>37</v>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="9" t="n">
-        <v>0.45</v>
+        <v>26.56</v>
       </c>
       <c r="L76" s="7" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="M76" s="8" t="n">
-        <v>0.8</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N76" s="7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="O76" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0.74</v>
+        <v>33.03</v>
       </c>
       <c r="R76" s="4" t="inlineStr">
         <is>
@@ -6915,7 +6911,7 @@
         </is>
       </c>
       <c r="S76" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -6924,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -6932,11 +6928,7 @@
       <c r="X76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y76" s="4" t="inlineStr">
-        <is>
-          <t>2 x 100 % pumps per package</t>
-        </is>
-      </c>
+      <c r="Y76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -6944,22 +6936,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>X-102-PB</t>
+          <t>A-202-M2</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump B</t>
+          <t>Hvgo Product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
@@ -6976,52 +6968,52 @@
         </is>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0.75</v>
+        <v>37</v>
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="9" t="n">
-        <v>0.45</v>
+        <v>26.56</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="M77" s="8" t="n">
-        <v>0.8</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="O77" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0.74</v>
+        <v>33.03</v>
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S77" s="9" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="T77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U77" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>16.86</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X77" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y77" s="4" t="inlineStr"/>
     </row>
@@ -7031,17 +7023,17 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>X-103-PA</t>
+          <t>X-101-PA</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
+          <t>Demulsifier injection package - metering pump A</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -7122,17 +7114,17 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>X-103-PB</t>
+          <t>X-101-PB</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
+          <t>Demulsifier injection package - metering pump B</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7209,17 +7201,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>X-104-PA</t>
+          <t>X-102-PA</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
+          <t>Caustic injection package (desalted crude) - metering pump A</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -7300,17 +7292,17 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>X-104-PB</t>
+          <t>X-102-PB</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
+          <t>Caustic injection package (desalted crude) - metering pump B</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7387,22 +7379,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>DT-101A1</t>
+          <t>X-103-PA</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>D-101A</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
@@ -7410,7 +7402,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -7418,32 +7410,30 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I82" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J82" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I82" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J82" s="4" t="n"/>
       <c r="K82" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L82" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M82" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N82" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O82" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P82" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
@@ -7451,7 +7441,7 @@
         </is>
       </c>
       <c r="S82" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -7460,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -7470,7 +7460,7 @@
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
+          <t>2 x 100 % pumps per package</t>
         </is>
       </c>
     </row>
@@ -7480,22 +7470,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DT-101A2</t>
+          <t>X-103-PB</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>D-101A</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
@@ -7503,7 +7493,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -7511,61 +7501,55 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I83" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I83" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J83" s="4" t="n"/>
       <c r="K83" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M83" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P83" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S83" s="9" t="n">
-        <v>44.62</v>
+        <v>0</v>
       </c>
       <c r="T83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U83" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>27.66</v>
+        <v>0</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="4" t="inlineStr">
-        <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="Y83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -7573,22 +7557,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>DT-101B1</t>
+          <t>X-104-PA</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>D-101B</t>
+          <t>X-104</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
@@ -7596,7 +7580,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -7604,32 +7588,30 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I84" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I84" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J84" s="4" t="n"/>
       <c r="K84" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L84" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M84" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O84" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P84" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R84" s="4" t="inlineStr">
         <is>
@@ -7637,7 +7619,7 @@
         </is>
       </c>
       <c r="S84" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T84" s="9" t="n">
         <v>0</v>
@@ -7646,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -7656,7 +7638,7 @@
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
+          <t>2 x 100 % pumps per package</t>
         </is>
       </c>
     </row>
@@ -7666,22 +7648,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>DT-101B2</t>
+          <t>X-104-PB</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>D-101B</t>
+          <t>X-104</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
@@ -7689,7 +7671,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -7697,61 +7679,55 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I85" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J85" s="4" t="n"/>
       <c r="K85" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M85" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P85" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S85" s="9" t="n">
-        <v>44.62</v>
+        <v>0</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U85" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>27.66</v>
+        <v>0</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="4" t="inlineStr">
-        <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
-        </is>
-      </c>
+        <v>0.48</v>
+      </c>
+      <c r="Y85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -7759,18 +7735,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>MOV-A</t>
+          <t>DT-101A1</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr"/>
+          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>D-101A</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Valve actuators</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
@@ -7786,57 +7766,59 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I86" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J86" s="4" t="n"/>
+      <c r="I86" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K86" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="M86" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O86" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="P86" s="9" t="n">
-        <v>23.81</v>
+        <v>27.66</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>36</v>
+        <v>52.5</v>
       </c>
       <c r="R86" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
+        <v>44.62</v>
       </c>
       <c r="T86" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
-          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
         </is>
       </c>
     </row>
@@ -7846,18 +7828,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>MOV-B</t>
+          <t>DT-101A2</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>D-101A</t>
+        </is>
+      </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Valve actuators</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
@@ -7873,57 +7859,59 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I87" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J87" s="4" t="n"/>
+      <c r="I87" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K87" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="M87" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="P87" s="9" t="n">
-        <v>23.81</v>
+        <v>27.66</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>36</v>
+        <v>52.5</v>
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>44.62</v>
       </c>
       <c r="T87" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="X87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Y87" s="4" t="inlineStr">
         <is>
-          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
         </is>
       </c>
     </row>
@@ -7933,18 +7921,22 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HTP-101</t>
+          <t>DT-101B1</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr"/>
+          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>D-101B</t>
+        </is>
+      </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Heat tracing</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
@@ -7960,30 +7952,32 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I88" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="J88" s="4" t="n"/>
+      <c r="I88" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K88" s="9" t="n">
-        <v>21</v>
+        <v>44.62</v>
       </c>
       <c r="L88" s="7" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M88" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N88" s="7" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O88" s="9" t="n">
-        <v>21</v>
+        <v>44.62</v>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>21</v>
+        <v>52.5</v>
       </c>
       <c r="R88" s="4" t="inlineStr">
         <is>
@@ -7991,7 +7985,7 @@
         </is>
       </c>
       <c r="S88" s="9" t="n">
-        <v>21</v>
+        <v>44.62</v>
       </c>
       <c r="T88" s="9" t="n">
         <v>0</v>
@@ -8000,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -8010,7 +8004,7 @@
       </c>
       <c r="Y88" s="4" t="inlineStr">
         <is>
-          <t>Self-regulating; winter design -5 C; steam tracing elsewhere</t>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
         </is>
       </c>
     </row>
@@ -8020,18 +8014,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HTP-102</t>
+          <t>DT-101B2</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
+          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>D-101B</t>
+        </is>
+      </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Heat tracing</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
@@ -8047,30 +8045,32 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I89" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="J89" s="4" t="n"/>
+      <c r="I89" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K89" s="9" t="n">
-        <v>28</v>
+        <v>44.62</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M89" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O89" s="9" t="n">
-        <v>28</v>
+        <v>44.62</v>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>28</v>
+        <v>52.5</v>
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="S89" s="9" t="n">
-        <v>28</v>
+        <v>44.62</v>
       </c>
       <c r="T89" s="9" t="n">
         <v>0</v>
@@ -8087,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -8095,7 +8095,11 @@
       <c r="X89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y89" s="4" t="inlineStr"/>
+      <c r="Y89" s="4" t="inlineStr">
+        <is>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -8103,18 +8107,18 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>AH-101</t>
+          <t>MOV-A</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Valve actuators</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
@@ -8127,58 +8131,62 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I90" s="9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M90" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N90" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O90" s="9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="P90" s="9" t="n">
-        <v>7.44</v>
+        <v>23.81</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>14.12</v>
+        <v>36</v>
       </c>
       <c r="R90" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S90" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T90" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>7.44</v>
+        <v>0</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="X90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y90" s="4" t="inlineStr"/>
+      <c r="Y90" s="4" t="inlineStr">
+        <is>
+          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -8186,18 +8194,18 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>BEF-101A</t>
+          <t>MOV-B</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan A</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Valve actuators</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
@@ -8210,15 +8218,15 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I91" s="9" t="n">
-        <v>1.1</v>
+        <v>27</v>
       </c>
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="9" t="n">
-        <v>1.1</v>
+        <v>27</v>
       </c>
       <c r="L91" s="7" t="n">
         <v>1</v>
@@ -8227,41 +8235,45 @@
         <v>1</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>1.1</v>
+        <v>27</v>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0.82</v>
+        <v>23.81</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1.38</v>
+        <v>36</v>
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S91" s="9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T91" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="X91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y91" s="4" t="inlineStr"/>
+      <c r="Y91" s="4" t="inlineStr">
+        <is>
+          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -8269,18 +8281,18 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>BEF-101B</t>
+          <t>HTP-101</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan B</t>
+          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Heat tracing</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
@@ -8293,47 +8305,47 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1.1</v>
+        <v>30</v>
       </c>
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="9" t="n">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="L92" s="7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M92" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N92" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>1.1</v>
+        <v>21</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>1.38</v>
+        <v>21</v>
       </c>
       <c r="R92" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S92" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U92" s="9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
         <v>0</v>
@@ -8342,9 +8354,13 @@
         <v>0</v>
       </c>
       <c r="X92" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Y92" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y92" s="4" t="inlineStr">
+        <is>
+          <t>Self-regulating; winter design -5 C; steam tracing elsewhere</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -8352,18 +8368,18 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101A</t>
+          <t>HTP-102</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package A (2 x 100 %)</t>
+          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Heat tracing</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
@@ -8376,33 +8392,33 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I93" s="9" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="9" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M93" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="P93" s="9" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>56.47</v>
+        <v>28</v>
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
@@ -8410,7 +8426,7 @@
         </is>
       </c>
       <c r="S93" s="9" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -8419,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -8435,12 +8451,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101B</t>
+          <t>AH-101</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package B (2 x 100 %)</t>
+          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -8463,11 +8479,11 @@
         </is>
       </c>
       <c r="I94" s="9" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="9" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L94" s="7" t="n">
         <v>0.8</v>
@@ -8479,36 +8495,36 @@
         <v>0.85</v>
       </c>
       <c r="O94" s="9" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="P94" s="9" t="n">
-        <v>29.75</v>
+        <v>7.44</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>56.47</v>
+        <v>14.12</v>
       </c>
       <c r="R94" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U94" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X94" s="9" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="4" t="inlineStr"/>
     </row>
@@ -8518,12 +8534,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102A</t>
+          <t>BEF-101A</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan A</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -8546,29 +8562,29 @@
         </is>
       </c>
       <c r="I95" s="9" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M95" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="P95" s="9" t="n">
-        <v>12.39</v>
+        <v>0.82</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>23.53</v>
+        <v>1.38</v>
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
@@ -8576,7 +8592,7 @@
         </is>
       </c>
       <c r="S95" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="T95" s="9" t="n">
         <v>0</v>
@@ -8585,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>12.39</v>
+        <v>0.82</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -8601,12 +8617,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102B</t>
+          <t>BEF-101B</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan B</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -8629,29 +8645,29 @@
         </is>
       </c>
       <c r="I96" s="9" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="L96" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M96" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O96" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>12.39</v>
+        <v>0.82</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>23.53</v>
+        <v>1.38</v>
       </c>
       <c r="R96" s="4" t="inlineStr">
         <is>
@@ -8665,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="9" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="V96" s="9" t="n">
         <v>0</v>
@@ -8674,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="X96" s="9" t="n">
-        <v>12.39</v>
+        <v>0.82</v>
       </c>
       <c r="Y96" s="4" t="inlineStr"/>
     </row>
@@ -8684,26 +8700,26 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CR-A</t>
+          <t>HVAC-101A</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Field convenience receptacles (120 V), via LTR-101A</t>
+          <t>SS-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -8712,49 +8728,49 @@
         </is>
       </c>
       <c r="I97" s="9" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M97" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O97" s="9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="P97" s="9" t="n">
-        <v>4.84</v>
+        <v>29.75</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>11.11</v>
+        <v>56.47</v>
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="T97" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>29.75</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="X97" s="9" t="n">
         <v>0</v>
@@ -8767,26 +8783,26 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CR-B</t>
+          <t>HVAC-101B</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Field convenience receptacles (120 V), via LTR-101B</t>
+          <t>SS-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -8795,52 +8811,52 @@
         </is>
       </c>
       <c r="I98" s="9" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="L98" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M98" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N98" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O98" s="9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="P98" s="9" t="n">
-        <v>4.84</v>
+        <v>29.75</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>11.11</v>
+        <v>56.47</v>
       </c>
       <c r="R98" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T98" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U98" s="9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="X98" s="9" t="n">
-        <v>0</v>
+        <v>29.75</v>
       </c>
       <c r="Y98" s="4" t="inlineStr"/>
     </row>
@@ -8850,26 +8866,26 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LTG-A</t>
+          <t>HVAC-102A</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Area &amp; structure lighting (LED), via LTR-101A 480-208Y/120 V</t>
+          <t>FAR-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -8878,29 +8894,29 @@
         </is>
       </c>
       <c r="I99" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M99" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="O99" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P99" s="9" t="n">
-        <v>7.89</v>
+        <v>12.39</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>25.26</v>
+        <v>23.53</v>
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
@@ -8908,7 +8924,7 @@
         </is>
       </c>
       <c r="S99" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T99" s="9" t="n">
         <v>0</v>
@@ -8917,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>7.89</v>
+        <v>12.39</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -8933,26 +8949,26 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>LTG-B</t>
+          <t>HVAC-102B</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Area &amp; structure lighting (LED), via LTR-101B 480-208Y/120 V</t>
+          <t>FAR-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8961,52 +8977,52 @@
         </is>
       </c>
       <c r="I100" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L100" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M100" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="O100" s="9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P100" s="9" t="n">
-        <v>7.89</v>
+        <v>12.39</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>25.26</v>
+        <v>23.53</v>
       </c>
       <c r="R100" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S100" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>7.89</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X100" s="9" t="n">
-        <v>0</v>
+        <v>12.39</v>
       </c>
       <c r="Y100" s="4" t="inlineStr"/>
     </row>
@@ -9016,12 +9032,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LTG-BA</t>
+          <t>CR-A</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Building lighting SS-100 / FAR-100, via LTR-101A</t>
+          <t>Field convenience receptacles (120 V), via LTR-101A</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -9044,11 +9060,11 @@
         </is>
       </c>
       <c r="I101" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L101" s="7" t="n">
         <v>1</v>
@@ -9057,36 +9073,36 @@
         <v>1</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P101" s="9" t="n">
-        <v>1.64</v>
+        <v>4.84</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>5.26</v>
+        <v>11.11</v>
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S101" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T101" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="X101" s="9" t="n">
         <v>0</v>
@@ -9099,12 +9115,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>LTG-BB</t>
+          <t>CR-B</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Building lighting SS-100 / FAR-100, via LTR-101B</t>
+          <t>Field convenience receptacles (120 V), via LTR-101B</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
@@ -9127,11 +9143,11 @@
         </is>
       </c>
       <c r="I102" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>1</v>
@@ -9140,36 +9156,36 @@
         <v>1</v>
       </c>
       <c r="N102" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="O102" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1.64</v>
+        <v>4.84</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>5.26</v>
+        <v>11.11</v>
       </c>
       <c r="R102" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S102" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T102" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="X102" s="9" t="n">
         <v>0</v>
@@ -9182,12 +9198,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>SP-A</t>
+          <t>LTG-A</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Building small power &amp; receptacles, via LTR-101A</t>
+          <t>Area &amp; structure lighting (LED), via LTR-101A 480-208Y/120 V</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
@@ -9210,29 +9226,29 @@
         </is>
       </c>
       <c r="I103" s="9" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M103" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="O103" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="P103" s="9" t="n">
-        <v>2.91</v>
+        <v>7.89</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>6.67</v>
+        <v>25.26</v>
       </c>
       <c r="R103" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9256,7 @@
         </is>
       </c>
       <c r="S103" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -9249,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>2.91</v>
+        <v>7.89</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -9265,12 +9281,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>SP-B</t>
+          <t>LTG-B</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Building small power &amp; receptacles, via LTR-101B</t>
+          <t>Area &amp; structure lighting (LED), via LTR-101B 480-208Y/120 V</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
@@ -9293,29 +9309,29 @@
         </is>
       </c>
       <c r="I104" s="9" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L104" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M104" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N104" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="O104" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>2.91</v>
+        <v>7.89</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>6.67</v>
+        <v>25.26</v>
       </c>
       <c r="R104" s="4" t="inlineStr">
         <is>
@@ -9323,7 +9339,7 @@
         </is>
       </c>
       <c r="S104" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T104" s="9" t="n">
         <v>0</v>
@@ -9332,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2.91</v>
+        <v>7.89</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -9348,26 +9364,26 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>WR-A</t>
+          <t>LTG-BA</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
+          <t>Building lighting SS-100 / FAR-100, via LTR-101A</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Welding outlets</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -9376,11 +9392,11 @@
         </is>
       </c>
       <c r="I105" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="L105" s="7" t="n">
         <v>1</v>
@@ -9389,36 +9405,36 @@
         <v>1</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="O105" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="P105" s="9" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="Q105" s="6" t="n">
-        <v>107.14</v>
+        <v>1.64</v>
+      </c>
+      <c r="Q105" s="9" t="n">
+        <v>5.26</v>
       </c>
       <c r="R105" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T105" s="9" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>76.52</v>
+        <v>0</v>
       </c>
       <c r="X105" s="9" t="n">
         <v>0</v>
@@ -9431,26 +9447,26 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>WR-B</t>
+          <t>LTG-BB</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
+          <t>Building lighting SS-100 / FAR-100, via LTR-101B</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Welding outlets</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -9459,11 +9475,11 @@
         </is>
       </c>
       <c r="I106" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="L106" s="7" t="n">
         <v>1</v>
@@ -9472,36 +9488,36 @@
         <v>1</v>
       </c>
       <c r="N106" s="7" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="O106" s="9" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="P106" s="9" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="Q106" s="6" t="n">
-        <v>107.14</v>
+        <v>1.64</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>5.26</v>
       </c>
       <c r="R106" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T106" s="9" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>76.52</v>
+        <v>0</v>
       </c>
       <c r="X106" s="9" t="n">
         <v>0</v>
@@ -9514,26 +9530,26 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CP-101</t>
+          <t>SP-A</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
+          <t>Building small power &amp; receptacles, via LTR-101A</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Cathodic protection</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -9542,29 +9558,29 @@
         </is>
       </c>
       <c r="I107" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M107" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O107" s="9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="P107" s="9" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="R107" s="4" t="inlineStr">
         <is>
@@ -9572,7 +9588,7 @@
         </is>
       </c>
       <c r="S107" s="9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T107" s="9" t="n">
         <v>0</v>
@@ -9581,7 +9597,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -9597,57 +9613,57 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>BC-101A</t>
+          <t>SP-B</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
+          <t>Building small power &amp; receptacles, via LTR-101B</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I108" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L108" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="N108" s="7" t="n">
-        <v>0.85</v>
-      </c>
       <c r="O108" s="9" t="n">
-        <v>3.33</v>
+        <v>6</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>2.07</v>
+        <v>2.91</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>3.92</v>
+        <v>6.67</v>
       </c>
       <c r="R108" s="4" t="inlineStr">
         <is>
@@ -9655,7 +9671,7 @@
         </is>
       </c>
       <c r="S108" s="9" t="n">
-        <v>3.33</v>
+        <v>6</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -9664,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>2.07</v>
+        <v>2.91</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -9680,18 +9696,18 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>BC-101B</t>
+          <t>WR-A</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Welding outlets</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
@@ -9704,53 +9720,53 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I109" s="9" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="9" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M109" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O109" s="9" t="n">
-        <v>3.33</v>
+        <v>75</v>
       </c>
       <c r="P109" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>3.92</v>
+        <v>76.52</v>
+      </c>
+      <c r="Q109" s="6" t="n">
+        <v>107.14</v>
       </c>
       <c r="R109" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S109" s="9" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>0</v>
+        <v>76.52</v>
       </c>
       <c r="X109" s="9" t="n">
         <v>0</v>
@@ -9763,18 +9779,18 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A</t>
+          <t>WR-B</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Welding outlets</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
@@ -9787,15 +9803,15 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I110" s="9" t="n">
-        <v>34.03</v>
+        <v>75</v>
       </c>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="9" t="n">
-        <v>34.03</v>
+        <v>75</v>
       </c>
       <c r="L110" s="7" t="n">
         <v>1</v>
@@ -9804,36 +9820,36 @@
         <v>1</v>
       </c>
       <c r="N110" s="7" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="O110" s="9" t="n">
-        <v>34.03</v>
+        <v>75</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="Q110" s="9" t="n">
-        <v>35.82</v>
+        <v>76.52</v>
+      </c>
+      <c r="Q110" s="6" t="n">
+        <v>107.14</v>
       </c>
       <c r="R110" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S110" s="9" t="n">
-        <v>34.03</v>
+        <v>0</v>
       </c>
       <c r="T110" s="9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>11.19</v>
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>76.52</v>
       </c>
       <c r="X110" s="9" t="n">
         <v>0</v>
@@ -9846,18 +9862,18 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B</t>
+          <t>CP-101</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Cathodic protection</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
@@ -9870,33 +9886,33 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I111" s="9" t="n">
-        <v>34.03</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="9" t="n">
-        <v>34.03</v>
+        <v>6.4</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M111" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="O111" s="9" t="n">
-        <v>34.03</v>
+        <v>6.4</v>
       </c>
       <c r="P111" s="9" t="n">
-        <v>11.19</v>
+        <v>4.8</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>35.82</v>
+        <v>8</v>
       </c>
       <c r="R111" s="4" t="inlineStr">
         <is>
@@ -9904,7 +9920,7 @@
         </is>
       </c>
       <c r="S111" s="9" t="n">
-        <v>34.03</v>
+        <v>6.4</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -9913,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>11.19</v>
+        <v>4.8</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -9929,18 +9945,18 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HST-101</t>
+          <t>BC-101A</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>UPS / DC</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
@@ -9957,49 +9973,49 @@
         </is>
       </c>
       <c r="I112" s="9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L112" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M112" s="8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N112" s="7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O112" s="9" t="n">
-        <v>15</v>
+        <v>3.33</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>11.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>18.75</v>
+        <v>3.92</v>
       </c>
       <c r="R112" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="T112" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="X112" s="9" t="n">
         <v>0</v>
@@ -10012,22 +10028,18 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>SB-101</t>
+          <t>BC-101B</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>H-101</t>
-        </is>
-      </c>
+          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>UPS / DC</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
@@ -10048,196 +10060,532 @@
       </c>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M113" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N113" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O113" s="9" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P113" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q113" s="9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R113" s="4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="S113" s="9" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="W113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>UPS-101A</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>UPS / DC</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="L114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O114" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="P114" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="Q114" s="9" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="R114" s="4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="S114" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="W114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>UPS-101B</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>UPS / DC</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="L115" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O115" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="P115" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="Q115" s="9" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="R115" s="4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="S115" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="W115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>HST-101</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L116" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P116" s="9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q116" s="9" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="R116" s="4" t="inlineStr">
+        <is>
+          <t>Intermittent</t>
+        </is>
+      </c>
+      <c r="S116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="X116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>SB-101</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>H-101</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="L113" s="7" t="n">
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L117" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M113" s="8" t="n">
+      <c r="M117" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N113" s="7" t="n">
+      <c r="N117" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="O113" s="9" t="n">
+      <c r="O117" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="P113" s="9" t="n">
+      <c r="P117" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q113" s="9" t="n">
+      <c r="Q117" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="R113" s="4" t="inlineStr">
+      <c r="R117" s="4" t="inlineStr">
         <is>
           <t>Intermittent</t>
         </is>
       </c>
-      <c r="S113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" s="9" t="n">
+      <c r="S117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="U113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="9" t="n">
+      <c r="U117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="C115" s="10" t="inlineStr">
+      <c r="X117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>TOTAL (all buses)</t>
         </is>
       </c>
-      <c r="O115" s="11">
-        <f>SUM(O5:O113)</f>
+      <c r="O119" s="11">
+        <f>SUM(O5:O117)</f>
         <v/>
       </c>
-      <c r="P115" s="11">
-        <f>SUM(P5:P113)</f>
+      <c r="P119" s="11">
+        <f>SUM(P5:P117)</f>
         <v/>
       </c>
-      <c r="Q115" s="11">
-        <f>SUM(Q5:Q113)</f>
+      <c r="Q119" s="11">
+        <f>SUM(Q5:Q117)</f>
         <v/>
       </c>
-      <c r="S115" s="11">
-        <f>SUM(S5:S113)</f>
+      <c r="S119" s="11">
+        <f>SUM(S5:S117)</f>
         <v/>
       </c>
-      <c r="T115" s="11">
-        <f>SUM(T5:T113)</f>
+      <c r="T119" s="11">
+        <f>SUM(T5:T117)</f>
         <v/>
       </c>
-      <c r="U115" s="11">
-        <f>SUM(U5:U113)</f>
+      <c r="U119" s="11">
+        <f>SUM(U5:U117)</f>
         <v/>
       </c>
-      <c r="V115" s="11">
-        <f>SUM(V5:V113)</f>
+      <c r="V119" s="11">
+        <f>SUM(V5:V117)</f>
         <v/>
       </c>
-      <c r="W115" s="11">
-        <f>SUM(W5:W113)</f>
+      <c r="W119" s="11">
+        <f>SUM(W5:W117)</f>
         <v/>
       </c>
-      <c r="X115" s="11">
-        <f>SUM(X5:X113)</f>
+      <c r="X119" s="11">
+        <f>SUM(X5:X117)</f>
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="C117" s="12" t="inlineStr">
+    <row r="121">
+      <c r="C121" s="12" t="inlineStr">
         <is>
           <t>Maximum demand per bus = C + 0.3 x I + 0.1 x S (kW and kvar separately), kVA = vector sum</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="B118" s="13" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>Bus</t>
         </is>
       </c>
-      <c r="D118" s="13" t="inlineStr">
+      <c r="D122" s="13" t="inlineStr">
         <is>
           <t>MD kW (formula)</t>
         </is>
       </c>
-      <c r="E118" s="13" t="inlineStr">
+      <c r="E122" s="13" t="inlineStr">
         <is>
           <t>MD kvar (formula)</t>
         </is>
       </c>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F122" s="13" t="inlineStr">
         <is>
           <t>MD kVA (formula)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
+    <row r="123">
+      <c r="B123" t="inlineStr">
         <is>
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="D119" s="14">
-        <f>1*SUMIF($H$5:$H$113,B119,S$5:S$113)+0.3*SUMIF($H$5:$H$113,B119,T$5:T$113)+0.1*SUMIF($H$5:$H$113,B119,U$5:U$113)</f>
+      <c r="D123" s="14">
+        <f>1*SUMIF($H$5:$H$117,B123,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B123,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B123,U$5:U$117)</f>
         <v/>
       </c>
-      <c r="E119" s="14">
-        <f>1*SUMIF($H$5:$H$113,B119,V$5:V$113)+0.3*SUMIF($H$5:$H$113,B119,W$5:W$113)+0.1*SUMIF($H$5:$H$113,B119,X$5:X$113)</f>
+      <c r="E123" s="14">
+        <f>1*SUMIF($H$5:$H$117,B123,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B123,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B123,X$5:X$117)</f>
         <v/>
       </c>
-      <c r="F119" s="14">
-        <f>SQRT(D119^2+E119^2)</f>
+      <c r="F123" s="14">
+        <f>SQRT(D123^2+E123^2)</f>
         <v/>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
+    <row r="124">
+      <c r="B124" t="inlineStr">
         <is>
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="D120" s="14">
-        <f>1*SUMIF($H$5:$H$113,B120,S$5:S$113)+0.3*SUMIF($H$5:$H$113,B120,T$5:T$113)+0.1*SUMIF($H$5:$H$113,B120,U$5:U$113)</f>
+      <c r="D124" s="14">
+        <f>1*SUMIF($H$5:$H$117,B124,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B124,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B124,U$5:U$117)</f>
         <v/>
       </c>
-      <c r="E120" s="14">
-        <f>1*SUMIF($H$5:$H$113,B120,V$5:V$113)+0.3*SUMIF($H$5:$H$113,B120,W$5:W$113)+0.1*SUMIF($H$5:$H$113,B120,X$5:X$113)</f>
+      <c r="E124" s="14">
+        <f>1*SUMIF($H$5:$H$117,B124,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B124,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B124,X$5:X$117)</f>
         <v/>
       </c>
-      <c r="F120" s="14">
-        <f>SQRT(D120^2+E120^2)</f>
+      <c r="F124" s="14">
+        <f>SQRT(D124^2+E124^2)</f>
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" t="inlineStr">
+    <row r="125">
+      <c r="B125" t="inlineStr">
         <is>
           <t>SWG-102A</t>
         </is>
       </c>
-      <c r="D121" s="14">
-        <f>1*SUMIF($H$5:$H$113,B121,S$5:S$113)+0.3*SUMIF($H$5:$H$113,B121,T$5:T$113)+0.1*SUMIF($H$5:$H$113,B121,U$5:U$113)</f>
+      <c r="D125" s="14">
+        <f>1*SUMIF($H$5:$H$117,B125,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B125,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B125,U$5:U$117)</f>
         <v/>
       </c>
-      <c r="E121" s="14">
-        <f>1*SUMIF($H$5:$H$113,B121,V$5:V$113)+0.3*SUMIF($H$5:$H$113,B121,W$5:W$113)+0.1*SUMIF($H$5:$H$113,B121,X$5:X$113)</f>
+      <c r="E125" s="14">
+        <f>1*SUMIF($H$5:$H$117,B125,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B125,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B125,X$5:X$117)</f>
         <v/>
       </c>
-      <c r="F121" s="14">
-        <f>SQRT(D121^2+E121^2)</f>
+      <c r="F125" s="14">
+        <f>SQRT(D125^2+E125^2)</f>
         <v/>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" t="inlineStr">
+    <row r="126">
+      <c r="B126" t="inlineStr">
         <is>
           <t>SWG-102B</t>
         </is>
       </c>
-      <c r="D122" s="14">
-        <f>1*SUMIF($H$5:$H$113,B122,S$5:S$113)+0.3*SUMIF($H$5:$H$113,B122,T$5:T$113)+0.1*SUMIF($H$5:$H$113,B122,U$5:U$113)</f>
+      <c r="D126" s="14">
+        <f>1*SUMIF($H$5:$H$117,B126,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B126,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B126,U$5:U$117)</f>
         <v/>
       </c>
-      <c r="E122" s="14">
-        <f>1*SUMIF($H$5:$H$113,B122,V$5:V$113)+0.3*SUMIF($H$5:$H$113,B122,W$5:W$113)+0.1*SUMIF($H$5:$H$113,B122,X$5:X$113)</f>
+      <c r="E126" s="14">
+        <f>1*SUMIF($H$5:$H$117,B126,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B126,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B126,X$5:X$117)</f>
         <v/>
       </c>
-      <c r="F122" s="14">
-        <f>SQRT(D122^2+E122^2)</f>
+      <c r="F126" s="14">
+        <f>SQRT(D126^2+E126^2)</f>
         <v/>
       </c>
     </row>
@@ -10351,13 +10699,13 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1768.232562292428</v>
+        <v>1769.363851221813</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1082.429212400215</v>
+        <v>1083.5605013296</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>127</v>
@@ -10366,16 +10714,16 @@
         <v>558.803349892213</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1176.409547389436</v>
+        <v>1177.540836318821</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>641.054411192787</v>
+        <v>642.8418197733628</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1339.735116095248</v>
+        <v>1341.584148105499</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.8780911489564922</v>
+        <v>0.8777241725624669</v>
       </c>
     </row>
     <row r="6">
@@ -10390,13 +10738,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1777.948105149571</v>
+        <v>1779.079394078956</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1078.630067428932</v>
+        <v>1079.761356358317</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>124.1155428571429</v>
@@ -10405,16 +10753,16 @@
         <v>575.2024948634958</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1173.384979772424</v>
+        <v>1174.516268701809</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>632.331118425917</v>
+        <v>634.1185270064927</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1332.919710292148</v>
+        <v>1334.76393858169</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.8803118227693123</v>
+        <v>0.8799430631530557</v>
       </c>
     </row>
     <row r="7">
@@ -10432,7 +10780,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1820.757150810007</v>
+        <v>1903.154114160792</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>984.8092474923169</v>
@@ -10441,19 +10789,19 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>835.9479033176899</v>
+        <v>918.3448666684751</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1068.404037824086</v>
+        <v>1076.643734159165</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>523.5348775660588</v>
+        <v>528.2045286718385</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1189.779793099092</v>
+        <v>1199.233819742267</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.8979846892853579</v>
+        <v>0.8977763272141132</v>
       </c>
     </row>
     <row r="8">
@@ -10471,10 +10819,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1820.757150810007</v>
+        <v>1903.154114160792</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>835.9479033176899</v>
+        <v>918.3448666684751</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0</v>
@@ -10483,16 +10831,16 @@
         <v>984.8092474923169</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>934.4288280669216</v>
+        <v>1016.825791417707</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>486.9919194520457</v>
+        <v>533.6884305098438</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1053.716453479829</v>
+        <v>1148.37190445966</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.886793430036166</v>
+        <v>0.8854499030052037</v>
       </c>
     </row>
     <row r="9">
@@ -10512,16 +10860,16 @@
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="6" t="n">
-        <v>2256.577680687416</v>
+        <v>2265.959978841174</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1190.231465206557</v>
+        <v>1196.760021236136</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>2551.233774028626</v>
+        <v>2562.578618138185</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.8845044713891814</v>
+        <v>0.8842499359053747</v>
       </c>
     </row>
     <row r="10">
@@ -10541,16 +10889,16 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="6" t="n">
-        <v>2119.54765763707</v>
+        <v>2203.087222806535</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1144.616282614999</v>
+        <v>1193.171698596596</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2408.864609608056</v>
+        <v>2505.444474265055</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.8798948887301474</v>
+        <v>0.8793199152628542</v>
       </c>
     </row>
     <row r="11">
@@ -10570,16 +10918,16 @@
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>2274.630302132916</v>
+        <v>2284.087658671904</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1261.645353118951</v>
+        <v>1268.565622510304</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2601.094386681868</v>
+        <v>2612.721793668865</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.8744897200883925</v>
+        <v>0.8742177082178033</v>
       </c>
     </row>
     <row r="12">
@@ -10599,16 +10947,16 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="6" t="n">
-        <v>2136.504038898167</v>
+        <v>2220.711920588987</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1213.293259571899</v>
+        <v>1264.762000512392</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>2456.975791893519</v>
+        <v>2555.618193742198</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.8695665809762115</v>
+        <v>0.8689529312425158</v>
       </c>
     </row>
     <row r="13">
@@ -10623,13 +10971,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3546.180667442</v>
+        <v>3548.443245300769</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2161.059279829148</v>
+        <v>2163.321857687918</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>251.1155428571429</v>
@@ -10638,16 +10986,16 @@
         <v>1134.005844755709</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2349.794527161861</v>
+        <v>2352.057105020631</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1273.385529618705</v>
+        <v>1276.960346779856</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>2672.647568783087</v>
+        <v>2676.340851335301</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.8792010419210537</v>
+        <v>0.8788331665031098</v>
       </c>
     </row>
     <row r="14">
@@ -10665,28 +11013,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3641.514301620014</v>
+        <v>3806.308228321584</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1820.757150810007</v>
+        <v>1903.154114160792</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1820.757150810007</v>
+        <v>1903.154114160792</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2002.832865891007</v>
+        <v>2093.469525576872</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1010.526797018105</v>
+        <v>1061.892959181682</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>2243.324295812992</v>
+        <v>2347.388189302886</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.8927968504728252</v>
+        <v>0.8918292829097765</v>
       </c>
     </row>
     <row r="15">
@@ -10701,23 +11049,23 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="6" t="n">
-        <v>4411.134341031084</v>
+        <v>4504.799579260891</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2474.938612690851</v>
+        <v>2533.327623022697</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>5058.006258518454</v>
+        <v>5168.265482236658</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.8721093086039703</v>
+        <v>0.8716269693853573</v>
       </c>
     </row>
     <row r="18">
@@ -10805,13 +11153,13 @@
         <v>7</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4960.039010152341</v>
+        <v>5067.95387863957</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>6200.048762690426</v>
+        <v>6334.942348299463</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>66.13385346869788</v>
+        <v>67.57271838186092</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -10850,13 +11198,13 @@
         <v>5.75</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2672.647568783087</v>
+        <v>2676.340851335301</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3340.809460978859</v>
+        <v>3345.426064169126</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>89.08825229276957</v>
+        <v>89.21136171117669</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>

--- a/deliverables/05-electrical/CFU-000-EL-LDL-001_Electrical-Load-List.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-LDL-001_Electrical-Load-List.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y126"/>
+  <dimension ref="A1:Y128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1948,26 +1948,26 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="9" t="n">
         <v>3.91</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9" t="n">
         <v>2.73</v>
-      </c>
-      <c r="W19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Y19" s="4" t="inlineStr"/>
     </row>
@@ -2035,26 +2035,26 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="T20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U20" s="9" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="4" t="inlineStr"/>
     </row>
@@ -3140,14 +3140,14 @@
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="9" t="n">
-        <v>13.19</v>
+        <v>23.09</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>0.91</v>
@@ -3156,13 +3156,13 @@
         <v>0.85</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>14.5</v>
+        <v>25.37</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>8.98</v>
+        <v>15.72</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>17.06</v>
+        <v>29.85</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>14.5</v>
+        <v>25.37</v>
       </c>
       <c r="V33" s="9" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>8.98</v>
+        <v>15.72</v>
       </c>
       <c r="Y33" s="4" t="inlineStr"/>
     </row>
@@ -3227,14 +3227,14 @@
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="9" t="n">
-        <v>13.19</v>
+        <v>23.09</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0.91</v>
@@ -3243,13 +3243,13 @@
         <v>0.85</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>14.5</v>
+        <v>25.37</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>8.98</v>
+        <v>15.72</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>17.06</v>
+        <v>29.85</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.5</v>
+        <v>25.37</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>8.98</v>
+        <v>15.72</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -3891,17 +3891,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>P-201A</t>
+          <t>P-119A</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product pump A</t>
+          <t>Flare KO drum pump-out pump A</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>P-201A/B</t>
+          <t>P-119A/B</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3922,30 +3922,30 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I42" s="6" t="n">
-        <v>110</v>
+      <c r="I42" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="9" t="n">
-        <v>81.26000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.95</v>
+        <v>0.875</v>
       </c>
       <c r="N42" s="7" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>85.54000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="P42" s="9" t="n">
-        <v>48.48</v>
+        <v>4.58</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>98.31999999999999</v>
+        <v>8</v>
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="S42" s="9" t="n">
-        <v>85.54000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>48.48</v>
+        <v>4.58</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -3978,17 +3978,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>P-201B</t>
+          <t>P-119B</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product pump B</t>
+          <t>Flare KO drum pump-out pump B</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>P-201A/B</t>
+          <t>P-119A/B</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4009,30 +4009,30 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I43" s="6" t="n">
-        <v>110</v>
+      <c r="I43" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="9" t="n">
-        <v>81.26000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.95</v>
+        <v>0.875</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>85.54000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="P43" s="9" t="n">
-        <v>48.48</v>
+        <v>4.58</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>98.31999999999999</v>
+        <v>8</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="9" t="n">
-        <v>85.54000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="V43" s="9" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="X43" s="9" t="n">
-        <v>48.48</v>
+        <v>4.58</v>
       </c>
       <c r="Y43" s="4" t="inlineStr"/>
     </row>
@@ -4065,17 +4065,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>P-203A</t>
+          <t>P-201A</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Slop wax pump A</t>
+          <t>LVGO pumparound / product pump A</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>P-203A/B</t>
+          <t>P-201A/B</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4096,53 +4096,53 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>5.5</v>
+      <c r="I44" s="6" t="n">
+        <v>110</v>
       </c>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="9" t="n">
-        <v>4.65</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.875</v>
+        <v>0.95</v>
       </c>
       <c r="N44" s="7" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>5.32</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>3.71</v>
+        <v>48.48</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>6.48</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U44" s="9" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X44" s="9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="4" t="inlineStr"/>
     </row>
@@ -4152,17 +4152,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>P-203B</t>
+          <t>P-201B</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Slop wax pump B</t>
+          <t>LVGO pumparound / product pump B</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>P-203A/B</t>
+          <t>P-201A/B</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4183,53 +4183,53 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>5.5</v>
+      <c r="I45" s="6" t="n">
+        <v>110</v>
       </c>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="9" t="n">
-        <v>4.65</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.875</v>
+        <v>0.95</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>5.32</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="P45" s="9" t="n">
-        <v>3.71</v>
+        <v>48.48</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>6.48</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S45" s="9" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="T45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U45" s="9" t="n">
-        <v>0</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X45" s="9" t="n">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="Y45" s="4" t="inlineStr"/>
     </row>
@@ -4239,17 +4239,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>P-204A</t>
+          <t>P-203A</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench) pump A</t>
+          <t>Slop wax pump A</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>P-204A/B</t>
+          <t>P-203A/B</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -4270,53 +4270,53 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I46" s="6" t="n">
-        <v>132</v>
+      <c r="I46" s="9" t="n">
+        <v>5.5</v>
       </c>
       <c r="J46" s="4" t="n"/>
-      <c r="K46" s="6" t="n">
-        <v>112.28</v>
+      <c r="K46" s="9" t="n">
+        <v>4.65</v>
       </c>
       <c r="L46" s="7" t="n">
         <v>0.85</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.95</v>
+        <v>0.875</v>
       </c>
       <c r="N46" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>118.18</v>
+        <v>0.82</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>5.32</v>
       </c>
       <c r="P46" s="9" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>135.84</v>
+        <v>3.71</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>6.48</v>
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="6" t="n">
-        <v>118.18</v>
+      <c r="U46" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X46" s="9" t="n">
-        <v>66.98</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="4" t="inlineStr"/>
     </row>
@@ -4326,17 +4326,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>P-204B</t>
+          <t>P-203B</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench) pump B</t>
+          <t>Slop wax pump B</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>P-204A/B</t>
+          <t>P-203A/B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4357,53 +4357,53 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I47" s="6" t="n">
-        <v>132</v>
+      <c r="I47" s="9" t="n">
+        <v>5.5</v>
       </c>
       <c r="J47" s="4" t="n"/>
-      <c r="K47" s="6" t="n">
-        <v>112.28</v>
+      <c r="K47" s="9" t="n">
+        <v>4.65</v>
       </c>
       <c r="L47" s="7" t="n">
         <v>0.85</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.95</v>
+        <v>0.875</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>118.18</v>
+        <v>0.82</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>5.32</v>
       </c>
       <c r="P47" s="9" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v>135.84</v>
+        <v>3.71</v>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>6.48</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="S47" s="6" t="n">
-        <v>118.18</v>
+          <t>Standby</t>
+        </is>
+      </c>
+      <c r="S47" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U47" s="9" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>66.98</v>
+        <v>0</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X47" s="9" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Y47" s="4" t="inlineStr"/>
     </row>
@@ -4413,17 +4413,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>P-205A</t>
+          <t>P-204A</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Hotwell sour water pump A</t>
+          <t>Vacuum residue (incl. quench) pump A</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>P-205A/B</t>
+          <t>P-204A/B</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4444,30 +4444,30 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I48" s="9" t="n">
-        <v>3.7</v>
+      <c r="I48" s="6" t="n">
+        <v>132</v>
       </c>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="9" t="n">
-        <v>3.21</v>
+      <c r="K48" s="6" t="n">
+        <v>112.28</v>
       </c>
       <c r="L48" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N48" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="M48" s="8" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N48" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="O48" s="9" t="n">
-        <v>3.66</v>
+      <c r="O48" s="6" t="n">
+        <v>118.18</v>
       </c>
       <c r="P48" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q48" s="9" t="n">
-        <v>4.47</v>
+        <v>66.98</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>135.84</v>
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -4480,8 +4480,8 @@
       <c r="T48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="9" t="n">
-        <v>3.66</v>
+      <c r="U48" s="6" t="n">
+        <v>118.18</v>
       </c>
       <c r="V48" s="9" t="n">
         <v>0</v>
@@ -4490,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="X48" s="9" t="n">
-        <v>2.56</v>
+        <v>66.98</v>
       </c>
       <c r="Y48" s="4" t="inlineStr"/>
     </row>
@@ -4500,17 +4500,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>P-205B</t>
+          <t>P-204B</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hotwell sour water pump B</t>
+          <t>Vacuum residue (incl. quench) pump B</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>P-205A/B</t>
+          <t>P-204A/B</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4531,38 +4531,38 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n">
-        <v>3.7</v>
+      <c r="I49" s="6" t="n">
+        <v>132</v>
       </c>
       <c r="J49" s="4" t="n"/>
-      <c r="K49" s="9" t="n">
-        <v>3.21</v>
+      <c r="K49" s="6" t="n">
+        <v>112.28</v>
       </c>
       <c r="L49" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N49" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="M49" s="8" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="O49" s="9" t="n">
-        <v>3.66</v>
+      <c r="O49" s="6" t="n">
+        <v>118.18</v>
       </c>
       <c r="P49" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q49" s="9" t="n">
-        <v>4.47</v>
+        <v>66.98</v>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v>135.84</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="S49" s="9" t="n">
-        <v>3.66</v>
+      <c r="S49" s="6" t="n">
+        <v>118.18</v>
       </c>
       <c r="T49" s="9" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2.56</v>
+        <v>66.98</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -4587,17 +4587,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>P-206A</t>
+          <t>P-205A</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Hotwell slop oil pump A</t>
+          <t>Hotwell sour water pump A</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>P-206A/B</t>
+          <t>P-205A/B</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -4619,29 +4619,29 @@
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0.75</v>
+        <v>3.7</v>
       </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="9" t="n">
-        <v>0.16</v>
+        <v>3.21</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>0.22</v>
+        <v>0.87</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="N50" s="7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>0.2</v>
+        <v>3.66</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.17</v>
+        <v>2.56</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0.27</v>
+        <v>4.47</v>
       </c>
       <c r="R50" s="4" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0.2</v>
+        <v>3.66</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0.17</v>
+        <v>2.56</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -4674,17 +4674,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>P-206B</t>
+          <t>P-205B</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hotwell slop oil pump B</t>
+          <t>Hotwell sour water pump B</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>P-206A/B</t>
+          <t>P-205A/B</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4706,29 +4706,29 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>0.75</v>
+        <v>3.7</v>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="9" t="n">
-        <v>0.16</v>
+        <v>3.21</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.22</v>
+        <v>0.87</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>0.2</v>
+        <v>3.66</v>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0.17</v>
+        <v>2.56</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0.27</v>
+        <v>4.47</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="9" t="n">
-        <v>0.2</v>
+        <v>3.66</v>
       </c>
       <c r="V51" s="9" t="n">
         <v>0</v>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>0.17</v>
+        <v>2.56</v>
       </c>
       <c r="Y51" s="4" t="inlineStr"/>
     </row>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>K-101A</t>
+          <t>P-206A</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>H-101 forced-draft fan A</t>
+          <t>Hotwell slop oil pump A</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>K-101A/B</t>
+          <t>P-206A/B</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Fired-heater fans</t>
+          <t>Pumps</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
@@ -4793,29 +4793,29 @@
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>90</v>
+        <v>0.75</v>
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="9" t="n">
-        <v>73.72</v>
+        <v>0.16</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>0.82</v>
+        <v>0.22</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>78.84</v>
+        <v>0.2</v>
       </c>
       <c r="P52" s="9" t="n">
-        <v>46.78</v>
+        <v>0.17</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>91.68000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="9" t="n">
-        <v>78.84</v>
+        <v>0.2</v>
       </c>
       <c r="V52" s="9" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="X52" s="9" t="n">
-        <v>46.78</v>
+        <v>0.17</v>
       </c>
       <c r="Y52" s="4" t="inlineStr"/>
     </row>
@@ -4848,22 +4848,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>K-101B</t>
+          <t>P-206B</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>H-101 forced-draft fan B</t>
+          <t>Hotwell slop oil pump B</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>K-101A/B</t>
+          <t>P-206A/B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Fired-heater fans</t>
+          <t>Pumps</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
@@ -4880,29 +4880,29 @@
         </is>
       </c>
       <c r="I53" s="9" t="n">
-        <v>90</v>
+        <v>0.75</v>
       </c>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="9" t="n">
-        <v>73.72</v>
+        <v>0.16</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>0.82</v>
+        <v>0.22</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>78.84</v>
+        <v>0.2</v>
       </c>
       <c r="P53" s="9" t="n">
-        <v>46.78</v>
+        <v>0.17</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>91.68000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="S53" s="9" t="n">
-        <v>78.84</v>
+        <v>0.2</v>
       </c>
       <c r="T53" s="9" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>46.78</v>
+        <v>0.17</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -4935,22 +4935,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>A-101-M1</t>
+          <t>K-101A</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
+          <t>H-101 forced-draft fan A</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>A-101</t>
+          <t>K-101A/B</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Air-cooler fans</t>
+          <t>Fired-heater fans</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>VFD</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4967,11 +4967,11 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="9" t="n">
-        <v>45</v>
+        <v>73.72</v>
       </c>
       <c r="L54" s="7" t="n">
         <v>0.82</v>
@@ -4980,39 +4980,39 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>49.61</v>
+        <v>78.84</v>
       </c>
       <c r="P54" s="9" t="n">
-        <v>16.31</v>
+        <v>46.78</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>52.22</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S54" s="9" t="n">
-        <v>49.61</v>
+        <v>0</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U54" s="9" t="n">
-        <v>0</v>
+        <v>78.84</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>16.31</v>
+        <v>0</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X54" s="9" t="n">
-        <v>0</v>
+        <v>46.78</v>
       </c>
       <c r="Y54" s="4" t="inlineStr"/>
     </row>
@@ -5022,22 +5022,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>A-101-M2</t>
+          <t>K-101B</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
+          <t>H-101 forced-draft fan B</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A-101</t>
+          <t>K-101A/B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Air-cooler fans</t>
+          <t>Fired-heater fans</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>VFD</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -5054,11 +5054,11 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="9" t="n">
-        <v>45</v>
+        <v>73.72</v>
       </c>
       <c r="L55" s="7" t="n">
         <v>0.82</v>
@@ -5067,16 +5067,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>49.61</v>
+        <v>78.84</v>
       </c>
       <c r="P55" s="9" t="n">
-        <v>16.31</v>
+        <v>46.78</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>52.22</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="S55" s="9" t="n">
-        <v>49.61</v>
+        <v>78.84</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>16.31</v>
+        <v>46.78</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>A-101-M3</t>
+          <t>A-101-M1</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 1/6 (VFD)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>A-101-M4</t>
+          <t>A-101-M2</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 2/6 (VFD)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>A-101-M5</t>
+          <t>A-101-M3</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 3/6 (VFD)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>A-101-M6</t>
+          <t>A-101-M4</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
+          <t>Atm. overhead condenser - fan motor 4/6 (VFD)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>A-103-M1</t>
+          <t>A-101-M5</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 1/2</t>
+          <t>Atm. overhead condenser - fan motor 5/6 (VFD)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>A-103</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>VFD</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -5489,29 +5489,29 @@
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="9" t="n">
-        <v>7.5</v>
+        <v>45</v>
       </c>
       <c r="L60" s="7" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.91</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N60" s="7" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="O60" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="P60" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>52.22</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="S60" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -5544,17 +5544,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>A-103-M2</t>
+          <t>A-101-M6</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Kero cooler - fan motor 2/2</t>
+          <t>Atm. overhead condenser - fan motor 6/6 (VFD)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A-103</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>VFD</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5576,29 +5576,29 @@
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="9" t="n">
-        <v>7.5</v>
+        <v>45</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>0.91</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="P61" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>52.22</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="S61" s="9" t="n">
-        <v>8.24</v>
+        <v>49.61</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>5.11</v>
+        <v>16.31</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>A-104-M1</t>
+          <t>A-103-M1</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 1/2</t>
+          <t>Kero cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>A-104</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5663,14 +5663,14 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="9" t="n">
-        <v>14.89</v>
+        <v>7.5</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M62" s="8" t="n">
         <v>0.91</v>
@@ -5679,13 +5679,13 @@
         <v>0.85</v>
       </c>
       <c r="O62" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="P62" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>19.26</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="S62" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>A-104-M2</t>
+          <t>A-103-M2</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Diesel cooler - fan motor 2/2</t>
+          <t>Kero cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A-104</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5750,14 +5750,14 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="9" t="n">
-        <v>14.89</v>
+        <v>7.5</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M63" s="8" t="n">
         <v>0.91</v>
@@ -5766,13 +5766,13 @@
         <v>0.85</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="P63" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>19.26</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="S63" s="9" t="n">
-        <v>16.37</v>
+        <v>8.24</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>10.14</v>
+        <v>5.11</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>A-105-M1</t>
+          <t>A-104-M1</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 1/2</t>
+          <t>Diesel cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -5837,11 +5837,11 @@
         </is>
       </c>
       <c r="I64" s="9" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="9" t="n">
-        <v>24.23</v>
+        <v>14.89</v>
       </c>
       <c r="L64" s="7" t="n">
         <v>0.8100000000000001</v>
@@ -5853,13 +5853,13 @@
         <v>0.85</v>
       </c>
       <c r="O64" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>31.33</v>
+        <v>19.26</v>
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="S64" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -5892,17 +5892,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>A-105-M2</t>
+          <t>A-104-M2</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Ago cooler - fan motor 2/2</t>
+          <t>Diesel cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5924,11 +5924,11 @@
         </is>
       </c>
       <c r="I65" s="9" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="9" t="n">
-        <v>24.23</v>
+        <v>14.89</v>
       </c>
       <c r="L65" s="7" t="n">
         <v>0.8100000000000001</v>
@@ -5940,13 +5940,13 @@
         <v>0.85</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="P65" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>31.33</v>
+        <v>19.26</v>
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="S65" s="9" t="n">
-        <v>26.63</v>
+        <v>16.37</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>16.5</v>
+        <v>10.14</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -5979,17 +5979,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>A-106-M1</t>
+          <t>A-105-M1</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 1/2</t>
+          <t>Ago cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -6011,14 +6011,14 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="9" t="n">
-        <v>8.550000000000001</v>
+        <v>24.23</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M66" s="8" t="n">
         <v>0.91</v>
@@ -6027,13 +6027,13 @@
         <v>0.85</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="P66" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>11.06</v>
+        <v>31.33</v>
       </c>
       <c r="R66" s="4" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="S66" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -6066,17 +6066,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>A-106-M2</t>
+          <t>A-105-M2</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Stabiliser overhead condenser - fan motor 2/2</t>
+          <t>Ago cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6098,14 +6098,14 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="9" t="n">
-        <v>8.550000000000001</v>
+        <v>24.23</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M67" s="8" t="n">
         <v>0.91</v>
@@ -6114,13 +6114,13 @@
         <v>0.85</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="P67" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>11.06</v>
+        <v>31.33</v>
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="S67" s="9" t="n">
-        <v>9.4</v>
+        <v>26.63</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>5.83</v>
+        <v>16.5</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>A-107-M1</t>
+          <t>A-106-M1</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 1/4</t>
+          <t>Stabiliser overhead condenser - fan motor 1/2</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>A-107</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -6185,14 +6185,14 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="9" t="n">
-        <v>19.25</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="M68" s="8" t="n">
         <v>0.91</v>
@@ -6201,13 +6201,13 @@
         <v>0.85</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>21.16</v>
+        <v>9.4</v>
       </c>
       <c r="P68" s="9" t="n">
-        <v>13.11</v>
+        <v>5.83</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>24.89</v>
+        <v>11.06</v>
       </c>
       <c r="R68" s="4" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="S68" s="9" t="n">
-        <v>21.16</v>
+        <v>9.4</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>13.11</v>
+        <v>5.83</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -6240,17 +6240,17 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>A-107-M2</t>
+          <t>A-106-M2</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 2/4</t>
+          <t>Stabiliser overhead condenser - fan motor 2/2</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A-107</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6272,14 +6272,14 @@
         </is>
       </c>
       <c r="I69" s="9" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="9" t="n">
-        <v>19.25</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="M69" s="8" t="n">
         <v>0.91</v>
@@ -6288,13 +6288,13 @@
         <v>0.85</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>21.16</v>
+        <v>9.4</v>
       </c>
       <c r="P69" s="9" t="n">
-        <v>13.11</v>
+        <v>5.83</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>24.89</v>
+        <v>11.06</v>
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="S69" s="9" t="n">
-        <v>21.16</v>
+        <v>9.4</v>
       </c>
       <c r="T69" s="9" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>13.11</v>
+        <v>5.83</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -6327,12 +6327,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>A-107-M3</t>
+          <t>A-107-M1</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 3/4</t>
+          <t>Splitter overhead condenser - fan motor 1/4</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>A-107-M4</t>
+          <t>A-107-M2</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Splitter overhead condenser - fan motor 4/4</t>
+          <t>Splitter overhead condenser - fan motor 2/4</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>A-108-M1</t>
+          <t>A-107-M3</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 1/2</t>
+          <t>Splitter overhead condenser - fan motor 3/4</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -6537,10 +6537,10 @@
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="9" t="n">
-        <v>23.23</v>
+        <v>19.25</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M72" s="8" t="n">
         <v>0.91</v>
@@ -6549,13 +6549,13 @@
         <v>0.85</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>30.04</v>
+        <v>24.89</v>
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="S72" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -6588,17 +6588,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>A-108-M2</t>
+          <t>A-107-M4</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha product cooler - fan motor 2/2</t>
+          <t>Splitter overhead condenser - fan motor 4/4</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6624,10 +6624,10 @@
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="9" t="n">
-        <v>23.23</v>
+        <v>19.25</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M73" s="8" t="n">
         <v>0.91</v>
@@ -6636,13 +6636,13 @@
         <v>0.85</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="P73" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>30.04</v>
+        <v>24.89</v>
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="S73" s="9" t="n">
-        <v>25.53</v>
+        <v>21.16</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>15.82</v>
+        <v>13.11</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -6675,17 +6675,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>A-201-M1</t>
+          <t>A-108-M1</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 1/2</t>
+          <t>Heavy naphtha product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -6707,14 +6707,14 @@
         </is>
       </c>
       <c r="I74" s="9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="9" t="n">
-        <v>12.4</v>
+        <v>23.23</v>
       </c>
       <c r="L74" s="7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M74" s="8" t="n">
         <v>0.91</v>
@@ -6723,13 +6723,13 @@
         <v>0.85</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>13.62</v>
+        <v>25.53</v>
       </c>
       <c r="P74" s="9" t="n">
-        <v>8.44</v>
+        <v>15.82</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>16.02</v>
+        <v>30.04</v>
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="S74" s="9" t="n">
-        <v>13.62</v>
+        <v>25.53</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>8.44</v>
+        <v>15.82</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -6762,17 +6762,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>A-201-M2</t>
+          <t>A-108-M2</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Lvgo cooler - fan motor 2/2</t>
+          <t>Heavy naphtha product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -6794,14 +6794,14 @@
         </is>
       </c>
       <c r="I75" s="9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="9" t="n">
-        <v>12.4</v>
+        <v>23.23</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M75" s="8" t="n">
         <v>0.91</v>
@@ -6810,13 +6810,13 @@
         <v>0.85</v>
       </c>
       <c r="O75" s="9" t="n">
-        <v>13.62</v>
+        <v>25.53</v>
       </c>
       <c r="P75" s="9" t="n">
-        <v>8.44</v>
+        <v>15.82</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>16.02</v>
+        <v>30.04</v>
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="S75" s="9" t="n">
-        <v>13.62</v>
+        <v>25.53</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>8.44</v>
+        <v>15.82</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -6849,17 +6849,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>A-202-M1</t>
+          <t>A-201-M1</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 1/2</t>
+          <t>Lvgo cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6881,29 +6881,29 @@
         </is>
       </c>
       <c r="I76" s="9" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="9" t="n">
-        <v>26.56</v>
+        <v>12.4</v>
       </c>
       <c r="L76" s="7" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="M76" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N76" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O76" s="9" t="n">
-        <v>28.41</v>
+        <v>13.62</v>
       </c>
       <c r="P76" s="9" t="n">
-        <v>16.86</v>
+        <v>8.44</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>33.03</v>
+        <v>16.02</v>
       </c>
       <c r="R76" s="4" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="S76" s="9" t="n">
-        <v>28.41</v>
+        <v>13.62</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>16.86</v>
+        <v>8.44</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -6936,17 +6936,17 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>A-202-M2</t>
+          <t>A-201-M2</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Hvgo Product cooler - fan motor 2/2</t>
+          <t>Lvgo cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -6968,29 +6968,29 @@
         </is>
       </c>
       <c r="I77" s="9" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="9" t="n">
-        <v>26.56</v>
+        <v>12.4</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="M77" s="8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="O77" s="9" t="n">
-        <v>28.41</v>
+        <v>13.62</v>
       </c>
       <c r="P77" s="9" t="n">
-        <v>16.86</v>
+        <v>8.44</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>33.03</v>
+        <v>16.02</v>
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="S77" s="9" t="n">
-        <v>28.41</v>
+        <v>13.62</v>
       </c>
       <c r="T77" s="9" t="n">
         <v>0</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>16.86</v>
+        <v>8.44</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -7023,22 +7023,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>X-101-PA</t>
+          <t>A-202-M1</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump A</t>
+          <t>Hvgo Product cooler - fan motor 1/2</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -7055,29 +7055,29 @@
         </is>
       </c>
       <c r="I78" s="9" t="n">
-        <v>0.75</v>
+        <v>37</v>
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="9" t="n">
-        <v>0.45</v>
+        <v>26.56</v>
       </c>
       <c r="L78" s="7" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="M78" s="8" t="n">
-        <v>0.8</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N78" s="7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="O78" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0.74</v>
+        <v>33.03</v>
       </c>
       <c r="R78" s="4" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -7102,11 +7102,7 @@
       <c r="X78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y78" s="4" t="inlineStr">
-        <is>
-          <t>2 x 100 % pumps per package</t>
-        </is>
-      </c>
+      <c r="Y78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -7114,22 +7110,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>X-101-PB</t>
+          <t>A-202-M2</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Demulsifier injection package - metering pump B</t>
+          <t>Hvgo Product cooler - fan motor 2/2</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Chemical packages</t>
+          <t>Air-cooler fans</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
@@ -7146,52 +7142,52 @@
         </is>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0.75</v>
+        <v>37</v>
       </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="9" t="n">
-        <v>0.45</v>
+        <v>26.56</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="M79" s="8" t="n">
-        <v>0.8</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="O79" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.41</v>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0.48</v>
+        <v>16.86</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0.74</v>
+        <v>33.03</v>
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="T79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U79" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>16.86</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X79" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="4" t="inlineStr"/>
     </row>
@@ -7201,17 +7197,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>X-102-PA</t>
+          <t>X-101-PA</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump A</t>
+          <t>Demulsifier injection package - metering pump A</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -7259,26 +7255,26 @@
       </c>
       <c r="R80" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="9" t="n">
         <v>0.48</v>
-      </c>
-      <c r="W80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
@@ -7292,17 +7288,17 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>X-102-PB</t>
+          <t>X-101-PB</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude) - metering pump B</t>
+          <t>Demulsifier injection package - metering pump B</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7350,26 +7346,26 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S81" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U81" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="4" t="inlineStr"/>
     </row>
@@ -7379,17 +7375,17 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>X-103-PA</t>
+          <t>X-102-PA</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
+          <t>Caustic injection package (desalted crude) - metering pump A</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -7437,26 +7433,26 @@
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="9" t="n">
         <v>0.48</v>
-      </c>
-      <c r="W82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
@@ -7470,17 +7466,17 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>X-103-PB</t>
+          <t>X-102-PB</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
+          <t>Caustic injection package (desalted crude) - metering pump B</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7528,26 +7524,26 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U83" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="4" t="inlineStr"/>
     </row>
@@ -7557,17 +7553,17 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>X-104-PA</t>
+          <t>X-103-PA</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump A</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -7615,26 +7611,26 @@
       </c>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="9" t="n">
         <v>0.48</v>
-      </c>
-      <c r="W84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -7648,17 +7644,17 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>X-104-PB</t>
+          <t>X-103-PB</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
+          <t>Neutraliser / filming amine package (atm OH) - metering pump B</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -7706,26 +7702,26 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U85" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X85" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y85" s="4" t="inlineStr"/>
     </row>
@@ -7735,22 +7731,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>DT-101A1</t>
+          <t>X-104-PA</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump A</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>D-101A</t>
+          <t>X-104</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
@@ -7758,7 +7754,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -7766,59 +7762,57 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I86" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I86" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J86" s="4" t="n"/>
       <c r="K86" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M86" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O86" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P86" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R86" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S86" s="9" t="n">
-        <v>44.62</v>
+        <v>0</v>
       </c>
       <c r="T86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U86" s="9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>27.66</v>
+        <v>0</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="Y86" s="4" t="inlineStr">
         <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
+          <t>2 x 100 % pumps per package</t>
         </is>
       </c>
     </row>
@@ -7828,22 +7822,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>DT-101A2</t>
+          <t>X-104-PB</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>Corrosion inhibitor package (VDU OH) - metering pump B</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>D-101A</t>
+          <t>X-104</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Desalter transformers</t>
+          <t>Chemical packages</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
@@ -7851,7 +7845,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7859,32 +7853,30 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I87" s="6" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>150</v>
-      </c>
+      <c r="I87" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J87" s="4" t="n"/>
       <c r="K87" s="9" t="n">
-        <v>44.62</v>
+        <v>0.45</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M87" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P87" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>52.5</v>
+        <v>0.74</v>
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
@@ -7892,7 +7884,7 @@
         </is>
       </c>
       <c r="S87" s="9" t="n">
-        <v>44.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T87" s="9" t="n">
         <v>0</v>
@@ -7901,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>27.66</v>
+        <v>0.48</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -7909,11 +7901,7 @@
       <c r="X87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y87" s="4" t="inlineStr">
-        <is>
-          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
-        </is>
-      </c>
+      <c r="Y87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -7921,17 +7909,17 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>DT-101B1</t>
+          <t>DT-101A1</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>D-101A 1st stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>D-101B</t>
+          <t>D-101A</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -8014,17 +8002,17 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>DT-101B2</t>
+          <t>DT-101A2</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+          <t>D-101A 1st stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>D-101B</t>
+          <t>D-101A</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8107,18 +8095,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>MOV-A</t>
+          <t>DT-101B1</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr"/>
+          <t>D-101B 2nd stage - HV transformer 1/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>D-101B</t>
+        </is>
+      </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Valve actuators</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
@@ -8134,57 +8126,59 @@
           <t>MCC-101A</t>
         </is>
       </c>
-      <c r="I90" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J90" s="4" t="n"/>
+      <c r="I90" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K90" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="M90" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N90" s="7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O90" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="P90" s="9" t="n">
-        <v>23.81</v>
+        <v>27.66</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>36</v>
+        <v>52.5</v>
       </c>
       <c r="R90" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>44.62</v>
       </c>
       <c r="T90" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="X90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Y90" s="4" t="inlineStr">
         <is>
-          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
         </is>
       </c>
     </row>
@@ -8194,18 +8188,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>MOV-B</t>
+          <t>DT-101B2</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr"/>
+          <t>D-101B 2nd stage - HV transformer 2/2 (150 kVA, 480 V / 13-23 kV)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>D-101B</t>
+        </is>
+      </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Valve actuators</t>
+          <t>Desalter transformers</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
@@ -8221,57 +8219,59 @@
           <t>MCC-101B</t>
         </is>
       </c>
-      <c r="I91" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J91" s="4" t="n"/>
+      <c r="I91" s="6" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>150</v>
+      </c>
       <c r="K91" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="M91" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>27</v>
+        <v>44.62</v>
       </c>
       <c r="P91" s="9" t="n">
-        <v>23.81</v>
+        <v>27.66</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>36</v>
+        <v>52.5</v>
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
+        <v>44.62</v>
       </c>
       <c r="T91" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>27.66</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="X91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Y91" s="4" t="inlineStr">
         <is>
-          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+          <t>Load factor 0.35 typical for electrostatic grids (vendor to confirm)</t>
         </is>
       </c>
     </row>
@@ -8281,18 +8281,18 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>HTP-101</t>
+          <t>MOV-A</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus A</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Heat tracing</t>
+          <t>Valve actuators</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
@@ -8309,40 +8309,40 @@
         </is>
       </c>
       <c r="I92" s="9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L92" s="7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M92" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N92" s="7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="R92" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S92" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -8351,14 +8351,14 @@
         <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="X92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Y92" s="4" t="inlineStr">
         <is>
-          <t>Self-regulating; winter design -5 C; steam tracing elsewhere</t>
+          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
         </is>
       </c>
     </row>
@@ -8368,18 +8368,18 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>HTP-102</t>
+          <t>MOV-B</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
+          <t>MOV / electric valve actuators - allowance (18 x 1.5 kW), bus B</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Heat tracing</t>
+          <t>Valve actuators</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
@@ -8396,40 +8396,40 @@
         </is>
       </c>
       <c r="I93" s="9" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M93" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S93" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T93" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -8438,12 +8438,16 @@
         <v>0</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="X93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y93" s="4" t="inlineStr"/>
+      <c r="Y93" s="4" t="inlineStr">
+        <is>
+          <t>ROSOVs on hot/LPG pump suctions, BL &amp; heater isolation</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -8451,18 +8455,18 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>AH-101</t>
+          <t>HTP-101</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
+          <t>Electric heat tracing panel - CDU slop &amp; HN lines (allowance)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Heat tracing</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
@@ -8475,33 +8479,33 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I94" s="9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L94" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M94" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O94" s="9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P94" s="9" t="n">
-        <v>7.44</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>14.12</v>
+        <v>21</v>
       </c>
       <c r="R94" s="4" t="inlineStr">
         <is>
@@ -8509,7 +8513,7 @@
         </is>
       </c>
       <c r="S94" s="9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
@@ -8518,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>7.44</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -8526,7 +8530,11 @@
       <c r="X94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Y94" s="4" t="inlineStr"/>
+      <c r="Y94" s="4" t="inlineStr">
+        <is>
+          <t>Self-regulating; winter design -5 C; steam tracing elsewhere</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -8534,18 +8542,18 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>BEF-101A</t>
+          <t>HTP-102</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan A</t>
+          <t>Electric heat tracing panel - VDU slop wax / slop oil lines (allowance)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Heat tracing</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
@@ -8558,33 +8566,33 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1.1</v>
+        <v>40</v>
       </c>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="9" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M95" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>1.38</v>
+        <v>28</v>
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
@@ -8592,7 +8600,7 @@
         </is>
       </c>
       <c r="S95" s="9" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="T95" s="9" t="n">
         <v>0</v>
@@ -8601,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -8617,12 +8625,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>BEF-101B</t>
+          <t>AH-101</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>SS-100 battery-room exhaust fan B</t>
+          <t>Analyser house AH-101 HVAC &amp; utilities (analysers on UPS)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -8645,52 +8653,52 @@
         </is>
       </c>
       <c r="I96" s="9" t="n">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="9" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="L96" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M96" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O96" s="9" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0.82</v>
+        <v>7.44</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>1.38</v>
+        <v>14.12</v>
       </c>
       <c r="R96" s="4" t="inlineStr">
         <is>
-          <t>Standby</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S96" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U96" s="9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="9" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="4" t="inlineStr"/>
     </row>
@@ -8700,12 +8708,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101A</t>
+          <t>BEF-101A</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan A</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -8728,29 +8736,29 @@
         </is>
       </c>
       <c r="I97" s="9" t="n">
-        <v>60</v>
+        <v>1.1</v>
       </c>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M97" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O97" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="P97" s="9" t="n">
-        <v>29.75</v>
+        <v>0.82</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>56.47</v>
+        <v>1.38</v>
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
@@ -8758,7 +8766,7 @@
         </is>
       </c>
       <c r="S97" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="T97" s="9" t="n">
         <v>0</v>
@@ -8767,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>29.75</v>
+        <v>0.82</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -8783,12 +8791,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>HVAC-101B</t>
+          <t>BEF-101B</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>SS-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 battery-room exhaust fan B</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
@@ -8811,29 +8819,29 @@
         </is>
       </c>
       <c r="I98" s="9" t="n">
-        <v>60</v>
+        <v>1.1</v>
       </c>
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="L98" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M98" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N98" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O98" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="P98" s="9" t="n">
-        <v>29.75</v>
+        <v>0.82</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>56.47</v>
+        <v>1.38</v>
       </c>
       <c r="R98" s="4" t="inlineStr">
         <is>
@@ -8847,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="9" t="n">
-        <v>48</v>
+        <v>1.1</v>
       </c>
       <c r="V98" s="9" t="n">
         <v>0</v>
@@ -8856,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="9" t="n">
-        <v>29.75</v>
+        <v>0.82</v>
       </c>
       <c r="Y98" s="4" t="inlineStr"/>
     </row>
@@ -8866,12 +8874,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102A</t>
+          <t>HVAC-101A</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package A (2 x 100 %)</t>
+          <t>SS-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -8894,11 +8902,11 @@
         </is>
       </c>
       <c r="I99" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L99" s="7" t="n">
         <v>0.8</v>
@@ -8910,13 +8918,13 @@
         <v>0.85</v>
       </c>
       <c r="O99" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="P99" s="9" t="n">
-        <v>12.39</v>
+        <v>29.75</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>23.53</v>
+        <v>56.47</v>
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
@@ -8924,7 +8932,7 @@
         </is>
       </c>
       <c r="S99" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="T99" s="9" t="n">
         <v>0</v>
@@ -8933,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>12.39</v>
+        <v>29.75</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -8949,12 +8957,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>HVAC-102B</t>
+          <t>HVAC-101B</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>FAR-100 HVAC package B (2 x 100 %)</t>
+          <t>SS-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
@@ -8977,11 +8985,11 @@
         </is>
       </c>
       <c r="I100" s="9" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L100" s="7" t="n">
         <v>0.8</v>
@@ -8993,13 +9001,13 @@
         <v>0.85</v>
       </c>
       <c r="O100" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="P100" s="9" t="n">
-        <v>12.39</v>
+        <v>29.75</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>23.53</v>
+        <v>56.47</v>
       </c>
       <c r="R100" s="4" t="inlineStr">
         <is>
@@ -9013,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="V100" s="9" t="n">
         <v>0</v>
@@ -9022,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="X100" s="9" t="n">
-        <v>12.39</v>
+        <v>29.75</v>
       </c>
       <c r="Y100" s="4" t="inlineStr"/>
     </row>
@@ -9032,26 +9040,26 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CR-A</t>
+          <t>HVAC-102A</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Field convenience receptacles (120 V), via LTR-101A</t>
+          <t>FAR-100 HVAC package A (2 x 100 %)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -9060,49 +9068,49 @@
         </is>
       </c>
       <c r="I101" s="9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M101" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P101" s="9" t="n">
-        <v>4.84</v>
+        <v>12.39</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>11.11</v>
+        <v>23.53</v>
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T101" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>12.39</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="X101" s="9" t="n">
         <v>0</v>
@@ -9115,26 +9123,26 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CR-B</t>
+          <t>HVAC-102B</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Field convenience receptacles (120 V), via LTR-101B</t>
+          <t>FAR-100 HVAC package B (2 x 100 %)</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Lighting &amp; small power</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Feeder (via LTR)</t>
+          <t>Feeder</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -9143,52 +9151,52 @@
         </is>
       </c>
       <c r="I102" s="9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L102" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N102" s="7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O102" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P102" s="9" t="n">
-        <v>4.84</v>
+        <v>12.39</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>11.11</v>
+        <v>23.53</v>
       </c>
       <c r="R102" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Standby</t>
         </is>
       </c>
       <c r="S102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T102" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U102" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="X102" s="9" t="n">
-        <v>0</v>
+        <v>12.39</v>
       </c>
       <c r="Y102" s="4" t="inlineStr"/>
     </row>
@@ -9198,12 +9206,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>LTG-A</t>
+          <t>CR-A</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Area &amp; structure lighting (LED), via LTR-101A 480-208Y/120 V</t>
+          <t>Field convenience receptacles (120 V), via LTR-101A</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
@@ -9226,11 +9234,11 @@
         </is>
       </c>
       <c r="I103" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L103" s="7" t="n">
         <v>1</v>
@@ -9239,36 +9247,36 @@
         <v>1</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="O103" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="P103" s="9" t="n">
-        <v>7.89</v>
+        <v>4.84</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>25.26</v>
+        <v>11.11</v>
       </c>
       <c r="R103" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S103" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T103" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>7.89</v>
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="X103" s="9" t="n">
         <v>0</v>
@@ -9281,12 +9289,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>LTG-B</t>
+          <t>CR-B</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Area &amp; structure lighting (LED), via LTR-101B 480-208Y/120 V</t>
+          <t>Field convenience receptacles (120 V), via LTR-101B</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
@@ -9309,11 +9317,11 @@
         </is>
       </c>
       <c r="I104" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L104" s="7" t="n">
         <v>1</v>
@@ -9322,36 +9330,36 @@
         <v>1</v>
       </c>
       <c r="N104" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="O104" s="9" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>7.89</v>
+        <v>4.84</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>25.26</v>
+        <v>11.11</v>
       </c>
       <c r="R104" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S104" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T104" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>7.89</v>
+        <v>0</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="X104" s="9" t="n">
         <v>0</v>
@@ -9364,12 +9372,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>LTG-BA</t>
+          <t>LTG-A</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Building lighting SS-100 / FAR-100, via LTR-101A</t>
+          <t>Area &amp; structure lighting (LED), via LTR-101A 480-208Y/120 V</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
@@ -9392,11 +9400,11 @@
         </is>
       </c>
       <c r="I105" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="L105" s="7" t="n">
         <v>1</v>
@@ -9408,13 +9416,13 @@
         <v>0.95</v>
       </c>
       <c r="O105" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1.64</v>
+        <v>7.89</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>5.26</v>
+        <v>25.26</v>
       </c>
       <c r="R105" s="4" t="inlineStr">
         <is>
@@ -9422,7 +9430,7 @@
         </is>
       </c>
       <c r="S105" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -9431,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1.64</v>
+        <v>7.89</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -9447,12 +9455,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>LTG-BB</t>
+          <t>LTG-B</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Building lighting SS-100 / FAR-100, via LTR-101B</t>
+          <t>Area &amp; structure lighting (LED), via LTR-101B 480-208Y/120 V</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -9475,11 +9483,11 @@
         </is>
       </c>
       <c r="I106" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="L106" s="7" t="n">
         <v>1</v>
@@ -9491,13 +9499,13 @@
         <v>0.95</v>
       </c>
       <c r="O106" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1.64</v>
+        <v>7.89</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>5.26</v>
+        <v>25.26</v>
       </c>
       <c r="R106" s="4" t="inlineStr">
         <is>
@@ -9505,7 +9513,7 @@
         </is>
       </c>
       <c r="S106" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -9514,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1.64</v>
+        <v>7.89</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -9530,12 +9538,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>SP-A</t>
+          <t>LTG-BA</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Building small power &amp; receptacles, via LTR-101A</t>
+          <t>Building lighting SS-100 / FAR-100, via LTR-101A</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
@@ -9558,29 +9566,29 @@
         </is>
       </c>
       <c r="I107" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M107" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="O107" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2.91</v>
+        <v>1.64</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>6.67</v>
+        <v>5.26</v>
       </c>
       <c r="R107" s="4" t="inlineStr">
         <is>
@@ -9588,7 +9596,7 @@
         </is>
       </c>
       <c r="S107" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T107" s="9" t="n">
         <v>0</v>
@@ -9597,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2.91</v>
+        <v>1.64</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -9613,12 +9621,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>SP-B</t>
+          <t>LTG-BB</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Building small power &amp; receptacles, via LTR-101B</t>
+          <t>Building lighting SS-100 / FAR-100, via LTR-101B</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
@@ -9641,29 +9649,29 @@
         </is>
       </c>
       <c r="I108" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L108" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M108" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N108" s="7" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="O108" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>2.91</v>
+        <v>1.64</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>6.67</v>
+        <v>5.26</v>
       </c>
       <c r="R108" s="4" t="inlineStr">
         <is>
@@ -9671,7 +9679,7 @@
         </is>
       </c>
       <c r="S108" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -9680,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>2.91</v>
+        <v>1.64</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -9696,26 +9704,26 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>WR-A</t>
+          <t>SP-A</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
+          <t>Building small power &amp; receptacles, via LTR-101A</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Welding outlets</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -9724,49 +9732,49 @@
         </is>
       </c>
       <c r="I109" s="9" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="9" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M109" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O109" s="9" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="P109" s="9" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="Q109" s="6" t="n">
-        <v>107.14</v>
+        <v>2.91</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>6.67</v>
       </c>
       <c r="R109" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T109" s="9" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>76.52</v>
+        <v>0</v>
       </c>
       <c r="X109" s="9" t="n">
         <v>0</v>
@@ -9779,26 +9787,26 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>WR-B</t>
+          <t>SP-B</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
+          <t>Building small power &amp; receptacles, via LTR-101B</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Welding outlets</t>
+          <t>Lighting &amp; small power</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>480</v>
+        <v>208</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Feeder</t>
+          <t>Feeder (via LTR)</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -9807,49 +9815,49 @@
         </is>
       </c>
       <c r="I110" s="9" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="9" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="L110" s="7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M110" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N110" s="7" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O110" s="9" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="Q110" s="6" t="n">
-        <v>107.14</v>
+        <v>2.91</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>6.67</v>
       </c>
       <c r="R110" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S110" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T110" s="9" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>76.52</v>
+        <v>0</v>
       </c>
       <c r="X110" s="9" t="n">
         <v>0</v>
@@ -9862,18 +9870,18 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CP-101</t>
+          <t>WR-A</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus A</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Cathodic protection</t>
+          <t>Welding outlets</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
@@ -9890,49 +9898,49 @@
         </is>
       </c>
       <c r="I111" s="9" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="9" t="n">
-        <v>6.4</v>
+        <v>75</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M111" s="8" t="n">
         <v>1</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O111" s="9" t="n">
-        <v>6.4</v>
+        <v>75</v>
       </c>
       <c r="P111" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q111" s="9" t="n">
-        <v>8</v>
+        <v>76.52</v>
+      </c>
+      <c r="Q111" s="6" t="n">
+        <v>107.14</v>
       </c>
       <c r="R111" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S111" s="9" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="T111" s="9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>76.52</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>0</v>
@@ -9945,18 +9953,18 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>BC-101A</t>
+          <t>WR-B</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
+          <t>Welding receptacles 3 x 63 A, 480 V, bus B</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Welding outlets</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
@@ -9969,53 +9977,53 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>MCC-101A</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="I112" s="9" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="9" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="L112" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M112" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N112" s="7" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O112" s="9" t="n">
-        <v>3.33</v>
+        <v>75</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q112" s="9" t="n">
-        <v>3.92</v>
+        <v>76.52</v>
+      </c>
+      <c r="Q112" s="6" t="n">
+        <v>107.14</v>
       </c>
       <c r="R112" s="4" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Intermittent</t>
         </is>
       </c>
       <c r="S112" s="9" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="T112" s="9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>76.52</v>
       </c>
       <c r="X112" s="9" t="n">
         <v>0</v>
@@ -10028,18 +10036,18 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>BC-101B</t>
+          <t>CP-101</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
+          <t>Cathodic protection transformer-rectifier (buried piping / tank bottoms in plot)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>UPS / DC</t>
+          <t>Cathodic protection</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
@@ -10052,33 +10060,33 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>MCC-101B</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="I113" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="9" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="L113" s="7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M113" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N113" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O113" s="9" t="n">
-        <v>3.33</v>
+        <v>6.4</v>
       </c>
       <c r="P113" s="9" t="n">
-        <v>2.07</v>
+        <v>4.8</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>3.92</v>
+        <v>8</v>
       </c>
       <c r="R113" s="4" t="inlineStr">
         <is>
@@ -10086,7 +10094,7 @@
         </is>
       </c>
       <c r="S113" s="9" t="n">
-        <v>3.33</v>
+        <v>6.4</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -10095,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2.07</v>
+        <v>4.8</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -10111,12 +10119,12 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>UPS-101A</t>
+          <t>BC-101A</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>125 V DC battery charger A (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -10139,29 +10147,29 @@
         </is>
       </c>
       <c r="I114" s="9" t="n">
-        <v>34.03</v>
+        <v>6</v>
       </c>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="9" t="n">
-        <v>34.03</v>
+        <v>3</v>
       </c>
       <c r="L114" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M114" s="8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N114" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="O114" s="9" t="n">
-        <v>34.03</v>
+        <v>3.33</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>11.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>35.82</v>
+        <v>3.92</v>
       </c>
       <c r="R114" s="4" t="inlineStr">
         <is>
@@ -10169,7 +10177,7 @@
         </is>
       </c>
       <c r="S114" s="9" t="n">
-        <v>34.03</v>
+        <v>3.33</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -10178,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>11.19</v>
+        <v>2.07</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -10194,12 +10202,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>UPS-101B</t>
+          <t>BC-101B</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+          <t>125 V DC battery charger B (switchgear control), 2 x 100 %</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
@@ -10222,29 +10230,29 @@
         </is>
       </c>
       <c r="I115" s="9" t="n">
-        <v>34.03</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="9" t="n">
-        <v>34.03</v>
+        <v>3</v>
       </c>
       <c r="L115" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M115" s="8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N115" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="O115" s="9" t="n">
-        <v>34.03</v>
+        <v>3.33</v>
       </c>
       <c r="P115" s="9" t="n">
-        <v>11.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>35.82</v>
+        <v>3.92</v>
       </c>
       <c r="R115" s="4" t="inlineStr">
         <is>
@@ -10252,7 +10260,7 @@
         </is>
       </c>
       <c r="S115" s="9" t="n">
-        <v>34.03</v>
+        <v>3.33</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -10261,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>11.19</v>
+        <v>2.07</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -10277,18 +10285,18 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HST-101</t>
+          <t>UPS-101A</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+          <t>UPS-101A rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>UPS / DC</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
@@ -10305,11 +10313,11 @@
         </is>
       </c>
       <c r="I116" s="9" t="n">
-        <v>15</v>
+        <v>34.03</v>
       </c>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="9" t="n">
-        <v>15</v>
+        <v>34.03</v>
       </c>
       <c r="L116" s="7" t="n">
         <v>1</v>
@@ -10318,36 +10326,36 @@
         <v>1</v>
       </c>
       <c r="N116" s="7" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="O116" s="9" t="n">
-        <v>15</v>
+        <v>34.03</v>
       </c>
       <c r="P116" s="9" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>18.75</v>
+        <v>35.82</v>
       </c>
       <c r="R116" s="4" t="inlineStr">
         <is>
-          <t>Intermittent</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="S116" s="9" t="n">
-        <v>0</v>
+        <v>34.03</v>
       </c>
       <c r="T116" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>11.19</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="X116" s="9" t="n">
         <v>0</v>
@@ -10360,22 +10368,18 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>SB-101</t>
+          <t>UPS-101B</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>H-101</t>
-        </is>
-      </c>
+          <t>UPS-101B rectifier input (2 x 100 % 100 kVA, 50 % share + battery recharge)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>UPS / DC</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
@@ -10392,11 +10396,11 @@
         </is>
       </c>
       <c r="I117" s="9" t="n">
-        <v>6</v>
+        <v>34.03</v>
       </c>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="9" t="n">
-        <v>6</v>
+        <v>34.03</v>
       </c>
       <c r="L117" s="7" t="n">
         <v>1</v>
@@ -10405,164 +10409,296 @@
         <v>1</v>
       </c>
       <c r="N117" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O117" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="P117" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="Q117" s="9" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="R117" s="4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="S117" s="9" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="9" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="W117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>HST-101</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Monorail hoists P-101/P-102 maintenance (2 x 7.5 kW)</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101A</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="O117" s="9" t="n">
+      <c r="O118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P118" s="9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q118" s="9" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="R118" s="4" t="inlineStr">
+        <is>
+          <t>Intermittent</t>
+        </is>
+      </c>
+      <c r="S118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="U118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="X118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>SB-101</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>H-101 convection sootblowers (8 x 0.75 kW, electric retract)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>H-101</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>MCC-101B</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="P117" s="9" t="n">
+      <c r="J119" s="4" t="n"/>
+      <c r="K119" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L119" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O119" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P119" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q117" s="9" t="n">
+      <c r="Q119" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="R117" s="4" t="inlineStr">
+      <c r="R119" s="4" t="inlineStr">
         <is>
           <t>Intermittent</t>
         </is>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="9" t="n">
+      <c r="S119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" s="9" t="n">
+      <c r="U119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="X117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" s="4" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="C119" s="10" t="inlineStr">
+      <c r="X119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>TOTAL (all buses)</t>
         </is>
       </c>
-      <c r="O119" s="11">
-        <f>SUM(O5:O117)</f>
+      <c r="O121" s="11">
+        <f>SUM(O5:O119)</f>
         <v/>
       </c>
-      <c r="P119" s="11">
-        <f>SUM(P5:P117)</f>
+      <c r="P121" s="11">
+        <f>SUM(P5:P119)</f>
         <v/>
       </c>
-      <c r="Q119" s="11">
-        <f>SUM(Q5:Q117)</f>
+      <c r="Q121" s="11">
+        <f>SUM(Q5:Q119)</f>
         <v/>
       </c>
-      <c r="S119" s="11">
-        <f>SUM(S5:S117)</f>
+      <c r="S121" s="11">
+        <f>SUM(S5:S119)</f>
         <v/>
       </c>
-      <c r="T119" s="11">
-        <f>SUM(T5:T117)</f>
+      <c r="T121" s="11">
+        <f>SUM(T5:T119)</f>
         <v/>
       </c>
-      <c r="U119" s="11">
-        <f>SUM(U5:U117)</f>
+      <c r="U121" s="11">
+        <f>SUM(U5:U119)</f>
         <v/>
       </c>
-      <c r="V119" s="11">
-        <f>SUM(V5:V117)</f>
+      <c r="V121" s="11">
+        <f>SUM(V5:V119)</f>
         <v/>
       </c>
-      <c r="W119" s="11">
-        <f>SUM(W5:W117)</f>
+      <c r="W121" s="11">
+        <f>SUM(W5:W119)</f>
         <v/>
       </c>
-      <c r="X119" s="11">
-        <f>SUM(X5:X117)</f>
+      <c r="X121" s="11">
+        <f>SUM(X5:X119)</f>
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="C121" s="12" t="inlineStr">
+    <row r="123">
+      <c r="C123" s="12" t="inlineStr">
         <is>
           <t>Maximum demand per bus = C + 0.3 x I + 0.1 x S (kW and kvar separately), kVA = vector sum</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="13" t="inlineStr">
+    <row r="124">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>Bus</t>
         </is>
       </c>
-      <c r="D122" s="13" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>MD kW (formula)</t>
         </is>
       </c>
-      <c r="E122" s="13" t="inlineStr">
+      <c r="E124" s="13" t="inlineStr">
         <is>
           <t>MD kvar (formula)</t>
         </is>
       </c>
-      <c r="F122" s="13" t="inlineStr">
+      <c r="F124" s="13" t="inlineStr">
         <is>
           <t>MD kVA (formula)</t>
         </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>MCC-101A</t>
-        </is>
-      </c>
-      <c r="D123" s="14">
-        <f>1*SUMIF($H$5:$H$117,B123,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B123,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B123,U$5:U$117)</f>
-        <v/>
-      </c>
-      <c r="E123" s="14">
-        <f>1*SUMIF($H$5:$H$117,B123,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B123,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B123,X$5:X$117)</f>
-        <v/>
-      </c>
-      <c r="F123" s="14">
-        <f>SQRT(D123^2+E123^2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>MCC-101B</t>
-        </is>
-      </c>
-      <c r="D124" s="14">
-        <f>1*SUMIF($H$5:$H$117,B124,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B124,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B124,U$5:U$117)</f>
-        <v/>
-      </c>
-      <c r="E124" s="14">
-        <f>1*SUMIF($H$5:$H$117,B124,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B124,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B124,X$5:X$117)</f>
-        <v/>
-      </c>
-      <c r="F124" s="14">
-        <f>SQRT(D124^2+E124^2)</f>
-        <v/>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>SWG-102A</t>
+          <t>MCC-101A</t>
         </is>
       </c>
       <c r="D125" s="14">
-        <f>1*SUMIF($H$5:$H$117,B125,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B125,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B125,U$5:U$117)</f>
+        <f>1*SUMIF($H$5:$H$119,B125,S$5:S$119)+0.3*SUMIF($H$5:$H$119,B125,T$5:T$119)+0.1*SUMIF($H$5:$H$119,B125,U$5:U$119)</f>
         <v/>
       </c>
       <c r="E125" s="14">
-        <f>1*SUMIF($H$5:$H$117,B125,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B125,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B125,X$5:X$117)</f>
+        <f>1*SUMIF($H$5:$H$119,B125,V$5:V$119)+0.3*SUMIF($H$5:$H$119,B125,W$5:W$119)+0.1*SUMIF($H$5:$H$119,B125,X$5:X$119)</f>
         <v/>
       </c>
       <c r="F125" s="14">
@@ -10573,19 +10709,57 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>SWG-102B</t>
+          <t>MCC-101B</t>
         </is>
       </c>
       <c r="D126" s="14">
-        <f>1*SUMIF($H$5:$H$117,B126,S$5:S$117)+0.3*SUMIF($H$5:$H$117,B126,T$5:T$117)+0.1*SUMIF($H$5:$H$117,B126,U$5:U$117)</f>
+        <f>1*SUMIF($H$5:$H$119,B126,S$5:S$119)+0.3*SUMIF($H$5:$H$119,B126,T$5:T$119)+0.1*SUMIF($H$5:$H$119,B126,U$5:U$119)</f>
         <v/>
       </c>
       <c r="E126" s="14">
-        <f>1*SUMIF($H$5:$H$117,B126,V$5:V$117)+0.3*SUMIF($H$5:$H$117,B126,W$5:W$117)+0.1*SUMIF($H$5:$H$117,B126,X$5:X$117)</f>
+        <f>1*SUMIF($H$5:$H$119,B126,V$5:V$119)+0.3*SUMIF($H$5:$H$119,B126,W$5:W$119)+0.1*SUMIF($H$5:$H$119,B126,X$5:X$119)</f>
         <v/>
       </c>
       <c r="F126" s="14">
         <f>SQRT(D126^2+E126^2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SWG-102A</t>
+        </is>
+      </c>
+      <c r="D127" s="14">
+        <f>1*SUMIF($H$5:$H$119,B127,S$5:S$119)+0.3*SUMIF($H$5:$H$119,B127,T$5:T$119)+0.1*SUMIF($H$5:$H$119,B127,U$5:U$119)</f>
+        <v/>
+      </c>
+      <c r="E127" s="14">
+        <f>1*SUMIF($H$5:$H$119,B127,V$5:V$119)+0.3*SUMIF($H$5:$H$119,B127,W$5:W$119)+0.1*SUMIF($H$5:$H$119,B127,X$5:X$119)</f>
+        <v/>
+      </c>
+      <c r="F127" s="14">
+        <f>SQRT(D127^2+E127^2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SWG-102B</t>
+        </is>
+      </c>
+      <c r="D128" s="14">
+        <f>1*SUMIF($H$5:$H$119,B128,S$5:S$119)+0.3*SUMIF($H$5:$H$119,B128,T$5:T$119)+0.1*SUMIF($H$5:$H$119,B128,U$5:U$119)</f>
+        <v/>
+      </c>
+      <c r="E128" s="14">
+        <f>1*SUMIF($H$5:$H$119,B128,V$5:V$119)+0.3*SUMIF($H$5:$H$119,B128,W$5:W$119)+0.1*SUMIF($H$5:$H$119,B128,X$5:X$119)</f>
+        <v/>
+      </c>
+      <c r="F128" s="14">
+        <f>SQRT(D128^2+E128^2)</f>
         <v/>
       </c>
     </row>
@@ -10699,31 +10873,31 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1769.363851221813</v>
+        <v>1786.79259847456</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1083.5605013296</v>
+        <v>1092.734365615314</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>127</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>558.803349892213</v>
+        <v>567.058232859246</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1177.540836318821</v>
+        <v>1187.540188901239</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>642.8418197733628</v>
+        <v>649.3891870067431</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1341.584148105499</v>
+        <v>1353.498436074778</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.8777241725624669</v>
+        <v>0.8773857119075608</v>
       </c>
     </row>
     <row r="6">
@@ -10738,31 +10912,31 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1779.079394078956</v>
+        <v>1796.508141331703</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1079.761356358317</v>
+        <v>1088.01623932535</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>124.1155428571429</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>575.2024948634958</v>
+        <v>584.37635914921</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1174.516268701809</v>
+        <v>1183.688538097414</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>634.1185270064927</v>
+        <v>640.0170434457574</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1334.76393858169</v>
+        <v>1345.637533336612</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.8799430631530557</v>
+        <v>0.87964887183428</v>
       </c>
     </row>
     <row r="7">
@@ -10860,16 +11034,16 @@
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="6" t="n">
-        <v>2265.959978841174</v>
+        <v>2276.059324949416</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1196.760021236136</v>
+        <v>1203.569283158851</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>2562.578618138185</v>
+        <v>2574.689315248094</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.8842499359053747</v>
+        <v>0.8840131939298072</v>
       </c>
     </row>
     <row r="10">
@@ -10889,16 +11063,16 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="6" t="n">
-        <v>2203.087222806535</v>
+        <v>2212.351214896095</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1193.171698596596</v>
+        <v>1199.306155693431</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>2505.444474265055</v>
+        <v>2516.512100733153</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.8793199152628542</v>
+        <v>0.879133946644467</v>
       </c>
     </row>
     <row r="11">
@@ -10918,16 +11092,16 @@
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>2284.087658671904</v>
+        <v>2294.267799549011</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1268.565622510304</v>
+        <v>1275.783440148382</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2612.721793668865</v>
+        <v>2625.126305952592</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.8742177082178033</v>
+        <v>0.8739647286100694</v>
       </c>
     </row>
     <row r="12">
@@ -10947,16 +11121,16 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="6" t="n">
-        <v>2220.711920588987</v>
+        <v>2230.050024615264</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1264.762000512392</v>
+        <v>1271.264525035037</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>2555.618193742198</v>
+        <v>2566.950838037047</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.8689529312425158</v>
+        <v>0.8687544738178888</v>
       </c>
     </row>
     <row r="13">
@@ -10971,31 +11145,31 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3548.443245300769</v>
+        <v>3583.300739806264</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2163.321857687918</v>
+        <v>2180.750604940665</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>251.1155428571429</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1134.005844755709</v>
+        <v>1151.434592008456</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2352.057105020631</v>
+        <v>2371.228726998653</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1276.960346779856</v>
+        <v>1289.406230452501</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>2676.340851335301</v>
+        <v>2699.128396885443</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.8788331665031098</v>
+        <v>0.8785164609934238</v>
       </c>
     </row>
     <row r="14">
@@ -11049,23 +11223,23 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="6" t="n">
-        <v>4504.799579260891</v>
+        <v>4524.317824164275</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2533.327623022697</v>
+        <v>2547.04796518342</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>5168.265482236658</v>
+        <v>5192.003959069712</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.8716269693853573</v>
+        <v>0.8714010736183894</v>
       </c>
     </row>
     <row r="18">
@@ -11153,13 +11327,13 @@
         <v>7</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>5067.95387863957</v>
+        <v>5091.133424772506</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>6334.942348299463</v>
+        <v>6363.916780965633</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>67.57271838186092</v>
+        <v>67.88177899696674</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -11198,13 +11372,13 @@
         <v>5.75</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2676.340851335301</v>
+        <v>2699.128396885443</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3345.426064169126</v>
+        <v>3373.910496106804</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>89.21136171117669</v>
+        <v>89.97094656284811</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
